--- a/00_trazabilidad_fuentes/registro_fuentes_psut_guatemala.xlsx
+++ b/00_trazabilidad_fuentes/registro_fuentes_psut_guatemala.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_readme" sheetId="1" r:id="R0d3faea1d3154a32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_fuentes" sheetId="2" r:id="R82fa9e8fabd24935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_estado_modulos" sheetId="3" r:id="Rc6964ff97f004d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_catalogos" sheetId="4" r:id="R6c215438db694d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_localizadores" sheetId="5" r:id="R4256b441b7dd4c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_readme" sheetId="1" r:id="R6dcf02b116094b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_fuentes" sheetId="2" r:id="R9d9ffa70b1dc4249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_estado_modulos" sheetId="3" r:id="Rf7a2f193d714490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_catalogos" sheetId="4" r:id="R291d00c53cca4f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_localizadores" sheetId="5" r:id="Rf3943676a8984e7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -103,6 +103,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1E426B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD8EAF4"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -400,7 +405,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="87">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -604,6 +609,24 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -644,7 +667,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RegistroFuentes" displayName="RegistroFuentes" ref="A1:L29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RegistroFuentes" displayName="RegistroFuentes" ref="A1:L34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="fuente_id"/>
     <x:tableColumn id="2" name="institucion"/>
@@ -687,8 +710,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="LocalizadoresDocumentales" displayName="LocalizadoresDocumentales" ref="A3:K395" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:K395"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="LocalizadoresDocumentales" displayName="LocalizadoresDocumentales" ref="A3:K442" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:K442"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="tipo_registro"/>
     <x:tableColumn id="2" name="registro_id"/>
@@ -1001,7 +1024,7 @@
       </x:c>
       <x:c r="B9" s="33" t="n">
         <x:f>COUNTA('01_fuentes'!A2:A200)</x:f>
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="29"/>
       <x:c r="D9" s="29"/>
@@ -1014,7 +1037,7 @@
       </x:c>
       <x:c r="B10" s="33" t="n">
         <x:f>COUNTIF('01_fuentes'!I2:I200,"utilizada")</x:f>
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="29"/>
       <x:c r="D10" s="29"/>
@@ -1052,7 +1075,7 @@
         <x:v>Registros con documentación de localización</x:v>
       </x:c>
       <x:c r="B14" s="51" t="n">
-        <x:v>392</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1060,7 +1083,7 @@
         <x:v>Observaciones externas con identificador</x:v>
       </x:c>
       <x:c r="B15" s="53" t="n">
-        <x:v>233</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1076,7 +1099,39 @@
         <x:v>Claves NO sin valor numérico</x:v>
       </x:c>
       <x:c r="B17" s="55" t="n">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="83" t="str">
+        <x:v>Registros numéricos cotejados directamente</x:v>
+      </x:c>
+      <x:c r="B18" s="84" t="n">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="83" t="str">
+        <x:v>Celdas N2O fugitivo vacías cotejadas</x:v>
+      </x:c>
+      <x:c r="B19" s="84" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="83" t="str">
+        <x:v>Alcance del cotejo BEN</x:v>
+      </x:c>
+      <x:c r="B20" s="84" t="str">
+        <x:v>42 controles anuales y 5 componentes GAS 2019; no es una revisión exhaustiva del balance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="83" t="str">
+        <x:v>Ausencias y notaciones</x:v>
+      </x:c>
+      <x:c r="B21" s="84" t="str">
+        <x:v>En N2O fugitivo y 3.G/3.I/3.J, la fuente tiene celdas vacías. NO es una clasificación interna, sin cuantificación.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1143,9 +1198,9 @@
         <x:v>licencia_derechos</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="103" customHeight="1">
       <x:c r="A2" s="39" t="str">
-        <x:v>BEN_SERIE_2018_2024</x:v>
+        <x:v>MEM_BEN</x:v>
       </x:c>
       <x:c r="B2" s="40" t="str">
         <x:v>Ministerio de Energía y Minas (MEM)</x:v>
@@ -1166,13 +1221,13 @@
         <x:v>Flujos físicos por producto y rubro</x:v>
       </x:c>
       <x:c r="H2" s="40" t="str">
-        <x:v>Tablas del balance; extracción documentada</x:v>
+        <x:v>Muestra de 42 celdas en 7 años y 5 componentes GAS 2019; véase 04_localizadores</x:v>
       </x:c>
       <x:c r="I2" s="40" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="J2" s="40" t="str">
-        <x:v>Control físico de la serie 2018–2024; el año de referencia del producto es 2024.</x:v>
+        <x:v>Alias previo: BEN_SERIE_2018_2024. Flujos anuales 2018-2024 utilizados; cotejo directo limitado a las 47 celdas documentadas, no a toda la extracción. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. </x:v>
       </x:c>
       <x:c r="K2" s="40" t="str">
         <x:v>kBEP</x:v>
@@ -1523,9 +1578,9 @@
         <x:v>IPCC; consultar términos</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="77" customHeight="1">
       <x:c r="A12" s="39" t="str">
-        <x:v>CRT_1990_2022</x:v>
+        <x:v>UNFCCC_GTM_CRT_2024</x:v>
       </x:c>
       <x:c r="B12" s="40" t="str">
         <x:v>MARN / CMNUCC</x:v>
@@ -1546,13 +1601,13 @@
         <x:v>Actividad, emisiones, factores implícitos y notaciones</x:v>
       </x:c>
       <x:c r="H12" s="40" t="str">
-        <x:v>Table1.A, Table1.B y Table3</x:v>
+        <x:v>Table1.A(a)s1-s4; Table1.B.2; Table10s2-s4; celdas en 04_localizadores</x:v>
       </x:c>
       <x:c r="I12" s="40" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="J12" s="40" t="str">
-        <x:v>Serie oficial procesada; el año 2022 calibra el módulo de emisiones 2024.</x:v>
+        <x:v>Alias previo: CRT_1990_2022. Cotejados 156 factores de combustión, 5 actividades de refinación, 10 factores fugitivos y 50 emisiones agrícolas; 5 celdas de N2O fugitivo vacías. Factores 2022 prolongados a 2023-2024. No supone validación integral del inventario.</x:v>
       </x:c>
       <x:c r="K12" s="40" t="str">
         <x:v>TJ; kt; kg/TJ</x:v>
@@ -1599,9 +1654,9 @@
         <x:v>CMNUCC/MARN; consultar términos</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="75" customHeight="1">
       <x:c r="A14" s="39" t="str">
-        <x:v>BANGUAT_VAB_A</x:v>
+        <x:v>BANGUAT_SCN_2013</x:v>
       </x:c>
       <x:c r="B14" s="40" t="str">
         <x:v>Banco de Guatemala</x:v>
@@ -1610,7 +1665,7 @@
         <x:v>PIB por actividad económica a precios constantes de 2013</x:v>
       </x:c>
       <x:c r="D14" s="40" t="str">
-        <x:v>2022 y 2024</x:v>
+        <x:v>2018-2024</x:v>
       </x:c>
       <x:c r="E14" s="40" t="str">
         <x:v>https://banguat.gob.gt/sites/default/files/banguat/cuentasnac/PIB2013/resumidos/2.1_PIB_por_AE_constantes_AR2013.xlsx</x:v>
@@ -1622,13 +1677,13 @@
         <x:v>VAB real de CIIU A</x:v>
       </x:c>
       <x:c r="H14" s="40" t="str">
-        <x:v>Filas 2022 y 2024</x:v>
+        <x:v>Serie VAB agrícola 2018-2024 integrada; prolongación 2023-2024 / 2022</x:v>
       </x:c>
       <x:c r="I14" s="40" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="J14" s="40" t="str">
-        <x:v>Indicador temporal del método MT-01.</x:v>
+        <x:v>Alias previo: BANGUAT_VAB_A. VAB real usado para prolongar emisiones agrícolas de 2022 a 2023-2024 según NT-02. Fuente no reabierta en este cotejo de originales BEN/CRT.</x:v>
       </x:c>
       <x:c r="K14" s="40" t="str">
         <x:v>millones de quetzales de 2013</x:v>
@@ -2203,6 +2258,188 @@
       </x:c>
       <x:c r="L29" s="44" t="str">
         <x:v>Banco de Guatemala; consultar términos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
+      <x:c r="A30" s="85" t="str">
+        <x:v>METODO_PSUT</x:v>
+      </x:c>
+      <x:c r="B30" s="85" t="str">
+        <x:v>Autores de la cuenta</x:v>
+      </x:c>
+      <x:c r="C30" s="85" t="str">
+        <x:v>Reglas metodológicas PSUT</x:v>
+      </x:c>
+      <x:c r="D30" s="85" t="str">
+        <x:v>2018-2024</x:v>
+      </x:c>
+      <x:c r="E30" s="85" t="str"/>
+      <x:c r="F30" s="85" t="str">
+        <x:v>PSUT</x:v>
+      </x:c>
+      <x:c r="G30" s="85" t="str">
+        <x:v>Mapeo, fronteras, redondeo y catálogos</x:v>
+      </x:c>
+      <x:c r="H30" s="85" t="str">
+        <x:v>NT-01; DATOS_MODELO; PSUT_LARGA</x:v>
+      </x:c>
+      <x:c r="I30" s="85" t="str">
+        <x:v>utilizada</x:v>
+      </x:c>
+      <x:c r="J30" s="85" t="str">
+        <x:v>Fuente interna; no observación externa.</x:v>
+      </x:c>
+      <x:c r="K30" s="85" t="str">
+        <x:v>varias</x:v>
+      </x:c>
+      <x:c r="L30" s="85" t="str">
+        <x:v>Licencias del repositorio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="75" customHeight="1">
+      <x:c r="A31" s="85" t="str">
+        <x:v>METODO_EMISIONES</x:v>
+      </x:c>
+      <x:c r="B31" s="85" t="str">
+        <x:v>Autores de la cuenta</x:v>
+      </x:c>
+      <x:c r="C31" s="85" t="str">
+        <x:v>Reglas de emisiones directas</x:v>
+      </x:c>
+      <x:c r="D31" s="85" t="str">
+        <x:v>2018-2024</x:v>
+      </x:c>
+      <x:c r="E31" s="85" t="str"/>
+      <x:c r="F31" s="85" t="str">
+        <x:v>Emisiones</x:v>
+      </x:c>
+      <x:c r="G31" s="85" t="str">
+        <x:v>Ceros directos y correspondencias</x:v>
+      </x:c>
+      <x:c r="H31" s="85" t="str">
+        <x:v>NT-02; registros CERO_DIRECTO</x:v>
+      </x:c>
+      <x:c r="I31" s="85" t="str">
+        <x:v>utilizada</x:v>
+      </x:c>
+      <x:c r="J31" s="85" t="str">
+        <x:v>Cero metodológico; no procede de una celda numérica CRT.</x:v>
+      </x:c>
+      <x:c r="K31" s="85" t="str">
+        <x:v>kg/TJ</x:v>
+      </x:c>
+      <x:c r="L31" s="85" t="str">
+        <x:v>Licencias del repositorio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
+      <x:c r="A32" s="85" t="str">
+        <x:v>CONVERSION</x:v>
+      </x:c>
+      <x:c r="B32" s="85" t="str">
+        <x:v>Autores de la cuenta</x:v>
+      </x:c>
+      <x:c r="C32" s="85" t="str">
+        <x:v>Conversión de unidades de masa</x:v>
+      </x:c>
+      <x:c r="D32" s="85" t="str">
+        <x:v>2018-2024</x:v>
+      </x:c>
+      <x:c r="E32" s="85" t="str"/>
+      <x:c r="F32" s="85" t="str">
+        <x:v>Conversión</x:v>
+      </x:c>
+      <x:c r="G32" s="85" t="str">
+        <x:v>Kilogramos por kilotonelada</x:v>
+      </x:c>
+      <x:c r="H32" s="85" t="str">
+        <x:v>PARAMETROS; PAR_004</x:v>
+      </x:c>
+      <x:c r="I32" s="85" t="str">
+        <x:v>utilizada</x:v>
+      </x:c>
+      <x:c r="J32" s="85" t="str">
+        <x:v>Identidad de unidades: 1000000 kg por kt.</x:v>
+      </x:c>
+      <x:c r="K32" s="85" t="str">
+        <x:v>kg/kt</x:v>
+      </x:c>
+      <x:c r="L32" s="85" t="str">
+        <x:v>No aplica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="75" customHeight="1">
+      <x:c r="A33" s="85" t="str">
+        <x:v>CONTROL</x:v>
+      </x:c>
+      <x:c r="B33" s="85" t="str">
+        <x:v>Autores de la cuenta</x:v>
+      </x:c>
+      <x:c r="C33" s="85" t="str">
+        <x:v>Tolerancias de verificación</x:v>
+      </x:c>
+      <x:c r="D33" s="85" t="str">
+        <x:v>2018-2024</x:v>
+      </x:c>
+      <x:c r="E33" s="85" t="str"/>
+      <x:c r="F33" s="85" t="str">
+        <x:v>Verificación</x:v>
+      </x:c>
+      <x:c r="G33" s="85" t="str">
+        <x:v>Tolerancias PSUT y emisiones</x:v>
+      </x:c>
+      <x:c r="H33" s="85" t="str">
+        <x:v>PARAMETROS; PAR_007 y PAR_008</x:v>
+      </x:c>
+      <x:c r="I33" s="85" t="str">
+        <x:v>utilizada</x:v>
+      </x:c>
+      <x:c r="J33" s="85" t="str">
+        <x:v>Criterios internos de control; no datos observados.</x:v>
+      </x:c>
+      <x:c r="K33" s="85" t="str">
+        <x:v>TJ; kt</x:v>
+      </x:c>
+      <x:c r="L33" s="85" t="str">
+        <x:v>Licencias del repositorio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="75" customHeight="1">
+      <x:c r="A34" s="85" t="str">
+        <x:v>IPCC_AR5</x:v>
+      </x:c>
+      <x:c r="B34" s="85" t="str">
+        <x:v>IPCC</x:v>
+      </x:c>
+      <x:c r="C34" s="85" t="str">
+        <x:v>Quinto Informe de Evaluación, WG I: Climate Change 2013</x:v>
+      </x:c>
+      <x:c r="D34" s="85" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="E34" s="85" t="str">
+        <x:v>https://www.ipcc.ch/report/ar5/wg1/</x:v>
+      </x:c>
+      <x:c r="F34" s="85" t="str">
+        <x:v>CO2 equivalente</x:v>
+      </x:c>
+      <x:c r="G34" s="85" t="str">
+        <x:v>GWP100 CH4=28 y N2O=265</x:v>
+      </x:c>
+      <x:c r="H34" s="85" t="str">
+        <x:v>Capítulo 8, tabla 8.7; NT-02, sección 17</x:v>
+      </x:c>
+      <x:c r="I34" s="85" t="str">
+        <x:v>utilizada</x:v>
+      </x:c>
+      <x:c r="J34" s="85" t="str">
+        <x:v>Métrica AR5 sin retroalimentación clima-carbono; constantes existentes sin modificación.</x:v>
+      </x:c>
+      <x:c r="K34" s="85" t="str">
+        <x:v>kg CO2e/kg gas</x:v>
+      </x:c>
+      <x:c r="L34" s="85" t="str">
+        <x:v>IPCC; consultar términos</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2218,7 +2455,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2641eff94b5741ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f3d041bba8943a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2247,18 +2484,18 @@
         <x:v>criterio</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="45" customHeight="1">
       <x:c r="A2" s="46" t="str">
         <x:v>Cuenta física de energía</x:v>
       </x:c>
       <x:c r="B2" s="46" t="str">
-        <x:v>BEN 2024; serie BEN 2018–2024</x:v>
+        <x:v>MEM_BEN: balances anuales 2018-2024</x:v>
       </x:c>
       <x:c r="C2" s="46" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="D2" s="46" t="str">
-        <x:v>El BEN controla los totales; la serie se usa para contexto y automatización.</x:v>
+        <x:v>Flujos anuales del BEN; cotejo parcial de 42 controles y 5 componentes GAS 2019. Contradicciones de origen documentadas, sin cambiar valores.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2289,46 +2526,46 @@
         <x:v>Define flujos y fronteras sin forzar desagregaciones no observadas.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="60" customHeight="1">
       <x:c r="A5" s="46" t="str">
         <x:v>Emisiones energéticas</x:v>
       </x:c>
       <x:c r="B5" s="46" t="str">
-        <x:v>CRT 2022; BEN 2024</x:v>
+        <x:v>UNFCCC_GTM_CRT_2024; MEM_BEN; METODO_EMISIONES</x:v>
       </x:c>
       <x:c r="C5" s="46" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="D5" s="46" t="str">
-        <x:v>Factores implícitos del CRT aplicados a actividad del BEN.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>156 factores externos cotejados con celdas CRT 2018-2022; 2023-2024 conserva factores 2022. Limitaciones de promedios por grupo pendientes de decisión.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="46" t="str">
         <x:v>Emisiones fugitivas</x:v>
       </x:c>
       <x:c r="B6" s="46" t="str">
-        <x:v>CRT 2022; BEN 2022 y 2024</x:v>
+        <x:v>UNFCCC_GTM_CRT_2024; MEM_BEN</x:v>
       </x:c>
       <x:c r="C6" s="46" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="D6" s="46" t="str">
-        <x:v>Producción energética observada en B y factores implícitos disponibles.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Se conserva producción/mejoramiento de petróleo 1.B.2.a.ii. Originales distinguen refinación/almacenamiento 1.B.2.a.iv, no incorporada. N2O K12 vacío: NO es clasificación interna.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="46" t="str">
         <x:v>Agricultura no energética</x:v>
       </x:c>
       <x:c r="B7" s="46" t="str">
-        <x:v>CRT 2022 Table3; BANGUAT VAB 2022/2024</x:v>
+        <x:v>UNFCCC_GTM_CRT_2024 Table10s2-s4; BANGUAT_SCN_2013</x:v>
       </x:c>
       <x:c r="C7" s="46" t="str">
         <x:v>utilizada</x:v>
       </x:c>
       <x:c r="D7" s="46" t="str">
-        <x:v>Actualización experimental MT-01 por categoría y gas.</x:v>
+        <x:v>50 emisiones fuente cotejadas; 3.F residual coincide con fila36 y 3.H con fila38. 3.G/3.I/3.J están vacíos en la fuente; NO es interno. Prolongación VAB 2023-2024 sin cambio.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2376,7 +2613,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34a032423bb84d4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61c6a7d1592d4b0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2437,7 +2674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R319495ce951746a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5c2b6fdc3974f19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2461,7 +2698,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="59" t="str">
-        <x:v>Localizadores documentales de factores, emisiones agrícolas, refinación y VAB</x:v>
+        <x:v>Localizadores documentales: factores, agricultura, refinación, VAB y muestra BEN</x:v>
       </x:c>
       <x:c r="B1" s="59" t="str">
         <x:v>Localizadores documentales de factores, emisiones agrícolas, refinación y VAB</x:v>
@@ -2494,9 +2731,9 @@
         <x:v>Localizadores documentales de factores, emisiones agrícolas, refinación y VAB</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="61" t="str">
-        <x:v>Los identificadores externos remiten a registros de extracción; CERO_DIRECTO y las claves NO se documentan como reglas internas y no como celdas numéricas de las CRT.</x:v>
+        <x:v>Solo las notas que indican cotejo directo acreditan revisión de la celda original. Se conserva el resto de localizadores previos; no se afirma revisión exhaustiva de BEN ni CRT. Los archivos originales no se redistribuyen.</x:v>
       </x:c>
       <x:c r="B2" s="61" t="str">
         <x:v>Los identificadores externos remiten a registros de extracción; CERO_DIRECTO y las claves NO se documentan como reglas internas y no como celdas numéricas de las CRT.</x:v>
@@ -2564,7 +2801,7 @@
         <x:v>nota</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="75" customHeight="1">
       <x:c r="A4" s="69" t="str">
         <x:v>ACTIVIDAD_REFINACION_OBS</x:v>
       </x:c>
@@ -2591,13 +2828,13 @@
         <x:v>CRT1A|2018|1.A.1.b|AD</x:v>
       </x:c>
       <x:c r="J4" s="70" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.b|AD</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C38 (TJ); C39 repite el valor</x:v>
       </x:c>
       <x:c r="K4" s="71" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>Actividad de combustión de refinación CRT = 2077.9477 TJ; numerador del coeficiente frente al crudo procesado PSUT, no el crudo total. El salto 2018-2019 está presente en los originales; se conserva el dato. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="87" customHeight="1">
       <x:c r="A5" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2626,13 +2863,13 @@
         <x:v>CRT10|2018|CO2|3</x:v>
       </x:c>
       <x:c r="J5" s="73" t="str">
-        <x:v>Table10s2; registro CRT10|2018|CO2|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s2!AG30 (kt CO2); columna del año 2018</x:v>
       </x:c>
       <x:c r="K5" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>Emisión observada AG30=37.309224651999997 kt CO2; valor fuente y valor integrado coinciden. El total coincide con 3.H, Table10s2!AG38. 3.G (AG37), 3.I (AG39) y 3.J (AG40) están vacíos en la fuente; NO en las salidas es una clasificación interna de ausencia, no un cero ni una notación literal leída allí. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="75" customHeight="1">
       <x:c r="A6" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2661,13 +2898,13 @@
         <x:v>CRT10|2018|CH4|3</x:v>
       </x:c>
       <x:c r="J6" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2018|CH4|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AG30 (kt CH4); columna del año 2018</x:v>
       </x:c>
       <x:c r="K6" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Emisión observada AG30=182.95491823397649 kt CH4; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s3!AG36=5.2289792378324993 kt CH4, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="75" customHeight="1">
       <x:c r="A7" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2696,13 +2933,13 @@
         <x:v>CRT10|2018|CH4|3.A</x:v>
       </x:c>
       <x:c r="J7" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2018|CH4|3.A</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AG31 (kt CH4); columna del año 2018</x:v>
       </x:c>
       <x:c r="K7" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Emisión observada AG31=167.64548599999995 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="75" customHeight="1">
       <x:c r="A8" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2731,13 +2968,13 @@
         <x:v>CRT10|2018|CH4|3.B</x:v>
       </x:c>
       <x:c r="J8" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2018|CH4|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AG32 (kt CH4); columna del año 2018</x:v>
       </x:c>
       <x:c r="K8" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>Emisión observada AG32=5.9190698299999998 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="75" customHeight="1">
       <x:c r="A9" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2766,13 +3003,13 @@
         <x:v>CRT10|2018|CH4|3.C</x:v>
       </x:c>
       <x:c r="J9" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2018|CH4|3.C</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AG33 (kt CH4); columna del año 2018</x:v>
       </x:c>
       <x:c r="K9" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>Emisión observada AG33=0.73345698194999986 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="75" customHeight="1">
       <x:c r="A10" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2801,13 +3038,13 @@
         <x:v>CRT10|2018|CH4|3.E</x:v>
       </x:c>
       <x:c r="J10" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2018|CH4|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AG35 (kt CH4); columna del año 2018</x:v>
       </x:c>
       <x:c r="K10" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>Emisión observada AG35=3.4279261841939999 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="75" customHeight="1">
       <x:c r="A11" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2836,13 +3073,13 @@
         <x:v>CRT10|2018|N2O|3</x:v>
       </x:c>
       <x:c r="J11" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2018|N2O|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AG30 (kt N2O); columna del año 2018</x:v>
       </x:c>
       <x:c r="K11" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>Emisión observada AG30=6.8335855969946468 kt N2O; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s4!AG36=0.13556612838825 kt N2O, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="75" customHeight="1">
       <x:c r="A12" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2871,13 +3108,13 @@
         <x:v>CRT10|2018|N2O|3.B</x:v>
       </x:c>
       <x:c r="J12" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2018|N2O|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AG32 (kt N2O); columna del año 2018</x:v>
       </x:c>
       <x:c r="K12" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>Emisión observada AG32=0.86863459992357606 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="75" customHeight="1">
       <x:c r="A13" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2906,13 +3143,13 @@
         <x:v>CRT10|2018|N2O|3.D</x:v>
       </x:c>
       <x:c r="J13" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2018|N2O|3.D</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AG34 (kt N2O); columna del año 2018</x:v>
       </x:c>
       <x:c r="K13" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>Emisión observada AG34=5.5164003040390206 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
       <x:c r="A14" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -2941,13 +3178,13 @@
         <x:v>CRT10|2018|N2O|3.E</x:v>
       </x:c>
       <x:c r="J14" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2018|N2O|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AG35 (kt N2O); columna del año 2018</x:v>
       </x:c>
       <x:c r="K14" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>Emisión observada AG35=0.31298456464379998 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="75" customHeight="1">
       <x:c r="A15" s="72" t="str">
         <x:v>ACTIVIDAD_REFINACION_OBS</x:v>
       </x:c>
@@ -2974,13 +3211,13 @@
         <x:v>CRT1A|2019|1.A.1.b|AD</x:v>
       </x:c>
       <x:c r="J15" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.b|AD</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C38 (TJ); C39 repite el valor</x:v>
       </x:c>
       <x:c r="K15" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>Actividad de combustión de refinación CRT = 7.51205924 TJ; numerador del coeficiente frente al crudo procesado PSUT, no el crudo total. El salto 2018-2019 está presente en los originales; se conserva el dato. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="87" customHeight="1">
       <x:c r="A16" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3009,13 +3246,13 @@
         <x:v>CRT10|2019|CO2|3</x:v>
       </x:c>
       <x:c r="J16" s="73" t="str">
-        <x:v>Table10s2; registro CRT10|2019|CO2|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s2!AH30 (kt CO2); columna del año 2019</x:v>
       </x:c>
       <x:c r="K16" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>Emisión observada AH30=36.357714860000002 kt CO2; valor fuente y valor integrado coinciden. El total coincide con 3.H, Table10s2!AH38. 3.G (AH37), 3.I (AH39) y 3.J (AH40) están vacíos en la fuente; NO en las salidas es una clasificación interna de ausencia, no un cero ni una notación literal leída allí. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="75" customHeight="1">
       <x:c r="A17" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3044,13 +3281,13 @@
         <x:v>CRT10|2019|CH4|3</x:v>
       </x:c>
       <x:c r="J17" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2019|CH4|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AH30 (kt CH4); columna del año 2019</x:v>
       </x:c>
       <x:c r="K17" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>Emisión observada AH30=187.12062362434347 kt CH4; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s3!AH36=4.7060049398175003 kt CH4, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="75" customHeight="1">
       <x:c r="A18" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3079,13 +3316,13 @@
         <x:v>CRT10|2019|CH4|3.A</x:v>
       </x:c>
       <x:c r="J18" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2019|CH4|3.A</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AH31 (kt CH4); columna del año 2019</x:v>
       </x:c>
       <x:c r="K18" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>Emisión observada AH31=169.21920399999999 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="75" customHeight="1">
       <x:c r="A19" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3114,13 +3351,13 @@
         <x:v>CRT10|2019|CH4|3.B</x:v>
       </x:c>
       <x:c r="J19" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2019|CH4|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AH32 (kt CH4); columna del año 2019</x:v>
       </x:c>
       <x:c r="K19" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>Emisión observada AH32=6.0104797400000001 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="75" customHeight="1">
       <x:c r="A20" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3149,13 +3386,13 @@
         <x:v>CRT10|2019|CH4|3.C</x:v>
       </x:c>
       <x:c r="J20" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2019|CH4|3.C</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AH33 (kt CH4); columna del año 2019</x:v>
       </x:c>
       <x:c r="K20" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>Emisión observada AH33=0.76926686297999991 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="75" customHeight="1">
       <x:c r="A21" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3184,13 +3421,13 @@
         <x:v>CRT10|2019|CH4|3.E</x:v>
       </x:c>
       <x:c r="J21" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2019|CH4|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AH35 (kt CH4); columna del año 2019</x:v>
       </x:c>
       <x:c r="K21" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
+        <x:v>Emisión observada AH35=6.4156680815459994 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="75" customHeight="1">
       <x:c r="A22" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3219,13 +3456,13 @@
         <x:v>CRT10|2019|N2O|3</x:v>
       </x:c>
       <x:c r="J22" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2019|N2O|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AH30 (kt N2O); columna del año 2019</x:v>
       </x:c>
       <x:c r="K22" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>Emisión observada AH30=6.4074999911736672 kt N2O; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s4!AH36=0.12200753547675001 kt N2O, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="75" customHeight="1">
       <x:c r="A23" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3254,13 +3491,13 @@
         <x:v>CRT10|2019|N2O|3.B</x:v>
       </x:c>
       <x:c r="J23" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2019|N2O|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AH32 (kt N2O); columna del año 2019</x:v>
       </x:c>
       <x:c r="K23" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>Emisión observada AH32=0.88251054294668285 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="75" customHeight="1">
       <x:c r="A24" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3289,13 +3526,13 @@
         <x:v>CRT10|2019|N2O|3.D</x:v>
       </x:c>
       <x:c r="J24" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2019|N2O|3.D</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AH34 (kt N2O); columna del año 2019</x:v>
       </x:c>
       <x:c r="K24" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>Emisión observada AH34=4.8172035226960341 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="75" customHeight="1">
       <x:c r="A25" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3324,13 +3561,13 @@
         <x:v>CRT10|2019|N2O|3.E</x:v>
       </x:c>
       <x:c r="J25" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2019|N2O|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AH35 (kt N2O); columna del año 2019</x:v>
       </x:c>
       <x:c r="K25" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+        <x:v>Emisión observada AH35=0.58577839005419996 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="75" customHeight="1">
       <x:c r="A26" s="72" t="str">
         <x:v>ACTIVIDAD_REFINACION_OBS</x:v>
       </x:c>
@@ -3357,13 +3594,13 @@
         <x:v>CRT1A|2020|1.A.1.b|AD</x:v>
       </x:c>
       <x:c r="J26" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.b|AD</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C38 (TJ); C39 repite el valor</x:v>
       </x:c>
       <x:c r="K26" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+        <x:v>Actividad de combustión de refinación CRT = 2.18344286 TJ; numerador del coeficiente frente al crudo procesado PSUT, no el crudo total. El salto 2018-2019 está presente en los originales; se conserva el dato. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="87" customHeight="1">
       <x:c r="A27" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3392,13 +3629,13 @@
         <x:v>CRT10|2020|CO2|3</x:v>
       </x:c>
       <x:c r="J27" s="73" t="str">
-        <x:v>Table10s2; registro CRT10|2020|CO2|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s2!AI30 (kt CO2); columna del año 2020</x:v>
       </x:c>
       <x:c r="K27" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>Emisión observada AI30=39.370831000000003 kt CO2; valor fuente y valor integrado coinciden. El total coincide con 3.H, Table10s2!AI38. 3.G (AI37), 3.I (AI39) y 3.J (AI40) están vacíos en la fuente; NO en las salidas es una clasificación interna de ausencia, no un cero ni una notación literal leída allí. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="75" customHeight="1">
       <x:c r="A28" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3427,13 +3664,13 @@
         <x:v>CRT10|2020|CH4|3</x:v>
       </x:c>
       <x:c r="J28" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2020|CH4|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AI30 (kt CH4); columna del año 2020</x:v>
       </x:c>
       <x:c r="K28" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
+        <x:v>Emisión observada AI30=189.57283666847999 kt CH4; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s3!AI36=4.4652635984520002 kt CH4, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="75" customHeight="1">
       <x:c r="A29" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3462,13 +3699,13 @@
         <x:v>CRT10|2020|CH4|3.A</x:v>
       </x:c>
       <x:c r="J29" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2020|CH4|3.A</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AI31 (kt CH4); columna del año 2020</x:v>
       </x:c>
       <x:c r="K29" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>Emisión observada AI31=170.79298799999998 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
       <x:c r="A30" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3497,13 +3734,13 @@
         <x:v>CRT10|2020|CH4|3.B</x:v>
       </x:c>
       <x:c r="J30" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2020|CH4|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AI32 (kt CH4); columna del año 2020</x:v>
       </x:c>
       <x:c r="K30" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>Emisión observada AI32=6.1018922700000005 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="75" customHeight="1">
       <x:c r="A31" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3532,13 +3769,13 @@
         <x:v>CRT10|2020|CH4|3.C</x:v>
       </x:c>
       <x:c r="J31" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2020|CH4|3.C</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AI33 (kt CH4); columna del año 2020</x:v>
       </x:c>
       <x:c r="K31" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
+        <x:v>Emisión observada AI33=0.79179625833 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
       <x:c r="A32" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3567,13 +3804,13 @@
         <x:v>CRT10|2020|CH4|3.E</x:v>
       </x:c>
       <x:c r="J32" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2020|CH4|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AI35 (kt CH4); columna del año 2020</x:v>
       </x:c>
       <x:c r="K32" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>Emisión observada AI35=7.4208965416980002 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="75" customHeight="1">
       <x:c r="A33" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3602,13 +3839,13 @@
         <x:v>CRT10|2020|N2O|3</x:v>
       </x:c>
       <x:c r="J33" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2020|N2O|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AI30 (kt N2O); columna del año 2020</x:v>
       </x:c>
       <x:c r="K33" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>Emisión observada AI30=5.3174063332614612 kt N2O; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s4!AI36=0.11576609329320002 kt N2O, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="75" customHeight="1">
       <x:c r="A34" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3637,13 +3874,13 @@
         <x:v>CRT10|2020|N2O|3.B</x:v>
       </x:c>
       <x:c r="J34" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2020|N2O|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AI32 (kt N2O); columna del año 2020</x:v>
       </x:c>
       <x:c r="K34" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>Emisión observada AI32=0.89638784022330209 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="75" customHeight="1">
       <x:c r="A35" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3672,13 +3909,13 @@
         <x:v>CRT10|2020|N2O|3.D</x:v>
       </x:c>
       <x:c r="J35" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2020|N2O|3.D</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AI34 (kt N2O); columna del año 2020</x:v>
       </x:c>
       <x:c r="K35" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>Emisión observada AI34=3.6276922807203595 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="75" customHeight="1">
       <x:c r="A36" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3707,13 +3944,13 @@
         <x:v>CRT10|2020|N2O|3.E</x:v>
       </x:c>
       <x:c r="J36" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2020|N2O|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AI35 (kt N2O); columna del año 2020</x:v>
       </x:c>
       <x:c r="K36" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>Emisión observada AI35=0.67756011902459989 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="75" customHeight="1">
       <x:c r="A37" s="72" t="str">
         <x:v>ACTIVIDAD_REFINACION_OBS</x:v>
       </x:c>
@@ -3740,13 +3977,13 @@
         <x:v>CRT1A|2021|1.A.1.b|AD</x:v>
       </x:c>
       <x:c r="J37" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.b|AD</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C38 (TJ); C39 repite el valor</x:v>
       </x:c>
       <x:c r="K37" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>Actividad de combustión de refinación CRT = 5.52012733 TJ; numerador del coeficiente frente al crudo procesado PSUT, no el crudo total. El salto 2018-2019 está presente en los originales; se conserva el dato. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="87" customHeight="1">
       <x:c r="A38" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3775,13 +4012,13 @@
         <x:v>CRT10|2021|CO2|3</x:v>
       </x:c>
       <x:c r="J38" s="73" t="str">
-        <x:v>Table10s2; registro CRT10|2021|CO2|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s2!AJ30 (kt CO2); columna del año 2021</x:v>
       </x:c>
       <x:c r="K38" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>Emisión observada AJ30=38.446130800000006 kt CO2; valor fuente y valor integrado coinciden. El total coincide con 3.H, Table10s2!AJ38. 3.G (AJ37), 3.I (AJ39) y 3.J (AJ40) están vacíos en la fuente; NO en las salidas es una clasificación interna de ausencia, no un cero ni una notación literal leída allí. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="75" customHeight="1">
       <x:c r="A39" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3810,13 +4047,13 @@
         <x:v>CRT10|2021|CH4|3</x:v>
       </x:c>
       <x:c r="J39" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2021|CH4|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AJ30 (kt CH4); columna del año 2021</x:v>
       </x:c>
       <x:c r="K39" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>Emisión observada AJ30=187.82836796209071 kt CH4; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s3!AJ36=4.6649076207547502 kt CH4, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="75" customHeight="1">
       <x:c r="A40" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3845,13 +4082,13 @@
         <x:v>CRT10|2021|CH4|3.A</x:v>
       </x:c>
       <x:c r="J40" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2021|CH4|3.A</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AJ31 (kt CH4); columna del año 2021</x:v>
       </x:c>
       <x:c r="K40" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>Emisión observada AJ31=172.36669699999999 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="75" customHeight="1">
       <x:c r="A41" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3880,13 +4117,13 @@
         <x:v>CRT10|2021|CH4|3.B</x:v>
       </x:c>
       <x:c r="J41" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2021|CH4|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AJ32 (kt CH4); columna del año 2021</x:v>
       </x:c>
       <x:c r="K41" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
+        <x:v>Emisión observada AJ32=6.0776549600000003 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="75" customHeight="1">
       <x:c r="A42" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3915,13 +4152,13 @@
         <x:v>CRT10|2021|CH4|3.C</x:v>
       </x:c>
       <x:c r="J42" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2021|CH4|3.C</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AJ33 (kt CH4); columna del año 2021</x:v>
       </x:c>
       <x:c r="K42" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
+        <x:v>Emisión observada AJ33=0.81432565367999998 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="75" customHeight="1">
       <x:c r="A43" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3950,13 +4187,13 @@
         <x:v>CRT10|2021|CH4|3.E</x:v>
       </x:c>
       <x:c r="J43" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2021|CH4|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AJ35 (kt CH4); columna del año 2021</x:v>
       </x:c>
       <x:c r="K43" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
+        <x:v>Emisión observada AJ35=3.9047827276559994 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="75" customHeight="1">
       <x:c r="A44" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -3985,13 +4222,13 @@
         <x:v>CRT10|2021|N2O|3</x:v>
       </x:c>
       <x:c r="J44" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2021|N2O|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AJ30 (kt N2O); columna del año 2021</x:v>
       </x:c>
       <x:c r="K44" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
+        <x:v>Emisión observada AJ30=4.8769202035825545 kt N2O; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s4!AJ36=0.12094204942697501 kt N2O, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="75" customHeight="1">
       <x:c r="A45" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4020,13 +4257,13 @@
         <x:v>CRT10|2021|N2O|3.B</x:v>
       </x:c>
       <x:c r="J45" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2021|N2O|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AJ32 (kt N2O); columna del año 2021</x:v>
       </x:c>
       <x:c r="K45" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
+        <x:v>Emisión observada AJ32=0.89302499766632615 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="75" customHeight="1">
       <x:c r="A46" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4055,13 +4292,13 @@
         <x:v>CRT10|2021|N2O|3.D</x:v>
       </x:c>
       <x:c r="J46" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2021|N2O|3.D</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AJ34 (kt N2O); columna del año 2021</x:v>
       </x:c>
       <x:c r="K46" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
+        <x:v>Emisión observada AJ34=3.5064295161380539 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="75" customHeight="1">
       <x:c r="A47" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4090,13 +4327,13 @@
         <x:v>CRT10|2021|N2O|3.E</x:v>
       </x:c>
       <x:c r="J47" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2021|N2O|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AJ35 (kt N2O); columna del año 2021</x:v>
       </x:c>
       <x:c r="K47" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
+        <x:v>Emisión observada AJ35=0.35652364035119993 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="75" customHeight="1">
       <x:c r="A48" s="72" t="str">
         <x:v>ACTIVIDAD_REFINACION_OBS</x:v>
       </x:c>
@@ -4123,13 +4360,13 @@
         <x:v>CRT1A|2022|1.A.1.b|AD</x:v>
       </x:c>
       <x:c r="J48" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.b|AD</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C38 (TJ); C39 repite el valor</x:v>
       </x:c>
       <x:c r="K48" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
+        <x:v>Actividad de combustión de refinación CRT = 24.02212068 TJ; numerador del coeficiente frente al crudo procesado PSUT, no el crudo total. El salto 2018-2019 está presente en los originales; se conserva el dato. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="87" customHeight="1">
       <x:c r="A49" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4158,13 +4395,13 @@
         <x:v>CRT10|2022|CO2|3</x:v>
       </x:c>
       <x:c r="J49" s="73" t="str">
-        <x:v>Table10s2; registro CRT10|2022|CO2|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s2!AK30 (kt CO2); columna del año 2022</x:v>
       </x:c>
       <x:c r="K49" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
+        <x:v>Emisión observada AK30=32.386982400000001 kt CO2; valor fuente y valor integrado coinciden. El total coincide con 3.H, Table10s2!AK38. 3.G (AK37), 3.I (AK39) y 3.J (AK40) están vacíos en la fuente; NO en las salidas es una clasificación interna de ausencia, no un cero ni una notación literal leída allí. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="75" customHeight="1">
       <x:c r="A50" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4193,13 +4430,13 @@
         <x:v>CRT10|2022|CH4|3</x:v>
       </x:c>
       <x:c r="J50" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2022|CH4|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AK30 (kt CH4); columna del año 2022</x:v>
       </x:c>
       <x:c r="K50" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
+        <x:v>Emisión observada AK30=189.77463780682595 kt CH4; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s3!AK36=4.4430659529390013 kt CH4, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="75" customHeight="1">
       <x:c r="A51" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4228,13 +4465,13 @@
         <x:v>CRT10|2022|CH4|3.A</x:v>
       </x:c>
       <x:c r="J51" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2022|CH4|3.A</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AK31 (kt CH4); columna del año 2022</x:v>
       </x:c>
       <x:c r="K51" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
+        <x:v>Emisión observada AK31=173.94042099999996 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="75" customHeight="1">
       <x:c r="A52" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4263,13 +4500,13 @@
         <x:v>CRT10|2022|CH4|3.B</x:v>
       </x:c>
       <x:c r="J52" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2022|CH4|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AK32 (kt CH4); columna del año 2022</x:v>
       </x:c>
       <x:c r="K52" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53">
+        <x:v>Emisión observada AK32=6.1690660199999998 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="75" customHeight="1">
       <x:c r="A53" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4298,13 +4535,13 @@
         <x:v>CRT10|2022|CH4|3.C</x:v>
       </x:c>
       <x:c r="J53" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2022|CH4|3.C</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AK33 (kt CH4); columna del año 2022</x:v>
       </x:c>
       <x:c r="K53" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
+        <x:v>Emisión observada AK33=0.83685504902999996 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="75" customHeight="1">
       <x:c r="A54" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4333,13 +4570,13 @@
         <x:v>CRT10|2022|CH4|3.E</x:v>
       </x:c>
       <x:c r="J54" s="73" t="str">
-        <x:v>Table10s3; registro CRT10|2022|CH4|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s3!AK35 (kt CH4); columna del año 2022</x:v>
       </x:c>
       <x:c r="K54" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
+        <x:v>Emisión observada AK35=4.3852297848570005 kt CH4; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="75" customHeight="1">
       <x:c r="A55" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4368,13 +4605,13 @@
         <x:v>CRT10|2022|N2O|3</x:v>
       </x:c>
       <x:c r="J55" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2022|N2O|3</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AK30 (kt N2O); columna del año 2022</x:v>
       </x:c>
       <x:c r="K55" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
+        <x:v>Emisión observada AK30=4.6504120427255868 kt N2O; valor fuente y valor integrado coinciden. El residual 3.F conservado coincide con el valor independiente Table10s4!AK36=0.11519059877990004 kt N2O, dentro de precisión numérica. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="75" customHeight="1">
       <x:c r="A56" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4403,13 +4640,13 @@
         <x:v>CRT10|2022|N2O|3.B</x:v>
       </x:c>
       <x:c r="J56" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2022|N2O|3.B</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AK32 (kt N2O); columna del año 2022</x:v>
       </x:c>
       <x:c r="K56" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
+        <x:v>Emisión observada AK32=0.90690116254555964 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="75" customHeight="1">
       <x:c r="A57" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4438,13 +4675,13 @@
         <x:v>CRT10|2022|N2O|3.D</x:v>
       </x:c>
       <x:c r="J57" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2022|N2O|3.D</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AK34 (kt N2O); columna del año 2022</x:v>
       </x:c>
       <x:c r="K57" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
+        <x:v>Emisión observada AK34=3.2279297358262267 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="75" customHeight="1">
       <x:c r="A58" s="72" t="str">
         <x:v>EMISION_AGRICULTURA_OBS</x:v>
       </x:c>
@@ -4473,10 +4710,10 @@
         <x:v>CRT10|2022|N2O|3.E</x:v>
       </x:c>
       <x:c r="J58" s="73" t="str">
-        <x:v>Table10s4; registro CRT10|2022|N2O|3.E</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table10s4!AK35 (kt N2O); columna del año 2022</x:v>
       </x:c>
       <x:c r="K58" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_10_series_tendencia_1990_2022_v01.csv.</x:v>
+        <x:v>Emisión observada AK35=0.40039054557390003 kt N2O; valor fuente y valor integrado coinciden. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -4682,7 +4919,7 @@
         <x:v>Cifra preliminar. Localizador recuperado del archivo de extracción banguat_pib_actividad_precios_constantes.xlsx.</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="75" customHeight="1">
       <x:c r="A66" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4711,13 +4948,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J66" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C37 (TJ), H37 (kt CO2)</x:v>
       </x:c>
       <x:c r="K66" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
+        <x:v>FE = (H37=5089.7212460000001 kt CO2 / C37=51094.912470000003 TJ) x 1000000 kg/kt; valor aplicado 99613.07300386105 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="75" customHeight="1">
       <x:c r="A67" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4746,13 +4983,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J67" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C37 (TJ), I37 (kt CH4)</x:v>
       </x:c>
       <x:c r="K67" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68">
+        <x:v>FE = (I37=1.5201971379999999 kt CH4 / C37=51094.912470000003 TJ) x 1000000 kg/kt; valor aplicado 29.75241691416092 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="75" customHeight="1">
       <x:c r="A68" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4781,13 +5018,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J68" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C37 (TJ), J37 (kt N2O)</x:v>
       </x:c>
       <x:c r="K68" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69">
+        <x:v>FE = (J37=0.202678411 kt N2O / C37=51094.912470000003 TJ) x 1000000 kg/kt; valor aplicado 3.966704339086619 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="75" customHeight="1">
       <x:c r="A69" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4816,13 +5053,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J69" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C33 (TJ), H33 (kt CO2)</x:v>
       </x:c>
       <x:c r="K69" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
+        <x:v>FE = (H33=5090.0167369999999 kt CO2 / C33=51780.43477 TJ) x 1000000 kg/kt; valor aplicado 98299.99998279272 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="75" customHeight="1">
       <x:c r="A70" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4851,13 +5088,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J70" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C33 (TJ), I33 (kt CH4)</x:v>
       </x:c>
       <x:c r="K70" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71">
+        <x:v>FE = (I33=0.051780435 kt CH4 / C33=51780.43477 TJ) x 1000000 kg/kt; valor aplicado 1.000000004441832 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="75" customHeight="1">
       <x:c r="A71" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4886,13 +5123,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J71" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C33 (TJ), J33 (kt N2O)</x:v>
       </x:c>
       <x:c r="K71" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
+        <x:v>FE = (J33=0.077670652000000007 kt N2O / C33=51780.43477 TJ) x 1000000 kg/kt; valor aplicado 1.4999999970065914 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="75" customHeight="1">
       <x:c r="A72" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4921,13 +5158,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J72" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C32 (TJ), H32 (kt CO2)</x:v>
       </x:c>
       <x:c r="K72" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73">
+        <x:v>FE = (H32=273.92226419999997 kt CO2 / C32=3541.6037430000001 TJ) x 1000000 kg/kt; valor aplicado 77344.13109919733 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="75" customHeight="1">
       <x:c r="A73" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4956,13 +5193,13 @@
         <x:v>CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J73" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C32 (TJ), I32 (kt CH4)</x:v>
       </x:c>
       <x:c r="K73" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74">
+        <x:v>FE = (I32=0.010624811 kt CH4 / C32=3541.6037430000001 TJ) x 1000000 kg/kt; valor aplicado 2.9999999353400275 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="75" customHeight="1">
       <x:c r="A74" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -4991,10 +5228,10 @@
         <x:v>CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J74" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C32 (TJ), J32 (kt N2O)</x:v>
       </x:c>
       <x:c r="K74" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J32=0.0021249620000000002 kt N2O / C32=3541.6037430000001 TJ) x 1000000 kg/kt; valor aplicado 0.599999930596414 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -5102,7 +5339,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_COMB|2018|1.A.1.a.i|GASEOUS_FUELS|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="75" customHeight="1">
       <x:c r="A78" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5131,13 +5368,13 @@
         <x:v>CRT1A|2018|1.A.1.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J78" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C39 (TJ), H39 (kt CO2)</x:v>
       </x:c>
       <x:c r="K78" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79">
+        <x:v>FE = (H39=153.97592399999999 kt CO2 / C39=2077.9477000000002 TJ) x 1000000 kg/kt; valor aplicado 74099.99972569088 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="75" customHeight="1">
       <x:c r="A79" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5166,13 +5403,13 @@
         <x:v>CRT1A|2018|1.A.1.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J79" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C39 (TJ), I39 (kt CH4)</x:v>
       </x:c>
       <x:c r="K79" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80">
+        <x:v>FE = (I39=0.00623384 kt CH4 / C39=2077.9477000000002 TJ) x 1000000 kg/kt; valor aplicado 2.9999985081433955 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="75" customHeight="1">
       <x:c r="A80" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5201,13 +5438,13 @@
         <x:v>CRT1A|2018|1.A.1.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J80" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2018|1.A.1.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s1!C39 (TJ), J39 (kt N2O)</x:v>
       </x:c>
       <x:c r="K80" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81">
+        <x:v>FE = (J39=0.0012467699999999999 kt N2O / C39=2077.9477000000002 TJ) x 1000000 kg/kt; valor aplicado 0.600000664116811 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="102" customHeight="1">
       <x:c r="A81" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5236,13 +5473,13 @@
         <x:v>CRT1A|2018|1.A.2|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J81" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2018|1.A.2|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s2!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K81" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82">
+        <x:v>FE = (H11=1943.671601 kt CO2 / C11=24474.11622 TJ) x 1000000 kg/kt; valor aplicado 79417.4377341418 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="87" customHeight="1">
       <x:c r="A82" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5271,13 +5508,13 @@
         <x:v>CRT1A|2018|1.A.2|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J82" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2018|1.A.2|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s2!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K82" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83">
+        <x:v>FE = (I11=0.065958000000000003 kt CH4 / C11=24474.11622 TJ) x 1000000 kg/kt; valor aplicado 2.695010492190921 kg CH4/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="87" customHeight="1">
       <x:c r="A83" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5306,13 +5543,13 @@
         <x:v>CRT1A|2018|1.A.2|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J83" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2018|1.A.2|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s2!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K83" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
+        <x:v>FE = (J11=0.012818384 kt N2O / C11=24474.11622 TJ) x 1000000 kg/kt; valor aplicado 0.5237526815993848 kg N2O/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="102" customHeight="1">
       <x:c r="A84" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5341,13 +5578,13 @@
         <x:v>CRT1A|2018|1.A.3|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J84" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2018|1.A.3|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s3!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K84" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85">
+        <x:v>FE = (H11=9683.1781127989998 kt CO2 / C11=135150.67123225998 TJ) x 1000000 kg/kt; valor aplicado 71647.28095325701 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="87" customHeight="1">
       <x:c r="A85" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5376,13 +5613,13 @@
         <x:v>CRT1A|2018|1.A.3|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J85" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2018|1.A.3|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s3!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K85" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86">
+        <x:v>FE = (I11=2.5335219549000003 kt CH4 / C11=135150.67123225998 TJ) x 1000000 kg/kt; valor aplicado 18.745907303309476 kg CH4/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="87" customHeight="1">
       <x:c r="A86" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5411,13 +5648,13 @@
         <x:v>CRT1A|2018|1.A.3|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J86" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2018|1.A.3|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s3!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K86" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87">
+        <x:v>FE = (J11=0.47828093200000005 kt N2O / C11=135150.67123225998 TJ) x 1000000 kg/kt; valor aplicado 3.5388720428776983 kg N2O/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="75" customHeight="1">
       <x:c r="A87" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5446,13 +5683,13 @@
         <x:v>CRT1A|2018|1.A.4.a|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J87" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C23 (TJ), H23 (kt CO2)</x:v>
       </x:c>
       <x:c r="K87" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88">
+        <x:v>FE = (H23=973.57529 kt CO2 / C23=8692.6365100000003 TJ) x 1000000 kg/kt; valor aplicado 112000.00010123511 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="75" customHeight="1">
       <x:c r="A88" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5481,13 +5718,13 @@
         <x:v>CRT1A|2018|1.A.4.a|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J88" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C23 (TJ), I23 (kt CH4)</x:v>
       </x:c>
       <x:c r="K88" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89">
+        <x:v>FE = (I23=2.6077909500000001 kt CH4 / C23=8692.6365100000003 TJ) x 1000000 kg/kt; valor aplicado 299.9999996548803 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="75" customHeight="1">
       <x:c r="A89" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5516,13 +5753,13 @@
         <x:v>CRT1A|2018|1.A.4.a|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J89" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C23 (TJ), J23 (kt N2O)</x:v>
       </x:c>
       <x:c r="K89" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90">
+        <x:v>FE = (J23=0.034770549999999997 kt N2O / C23=8692.6365100000003 TJ) x 1000000 kg/kt; valor aplicado 4.000000455557988 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="75" customHeight="1">
       <x:c r="A90" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5551,13 +5788,13 @@
         <x:v>CRT1A|2018|1.A.4.a|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J90" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C18 (TJ), H18 (kt CO2)</x:v>
       </x:c>
       <x:c r="K90" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91">
+        <x:v>FE = (H18=47.993509400000001 kt CO2 / C18=725.90181900000005 TJ) x 1000000 kg/kt; valor aplicado 66115.70345162615 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="75" customHeight="1">
       <x:c r="A91" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5586,13 +5823,13 @@
         <x:v>CRT1A|2018|1.A.4.a|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J91" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C18 (TJ), I18 (kt CH4)</x:v>
       </x:c>
       <x:c r="K91" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92">
+        <x:v>FE = (I18=0.0053928500000000002 kt CH4 / C18=725.90181900000005 TJ) x 1000000 kg/kt; valor aplicado 7.429172732242458 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="75" customHeight="1">
       <x:c r="A92" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5621,13 +5858,13 @@
         <x:v>CRT1A|2018|1.A.4.a|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J92" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.a|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C18 (TJ), J18 (kt N2O)</x:v>
       </x:c>
       <x:c r="K92" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93">
+        <x:v>FE = (J18=0.00024892000000000002 kt N2O / C18=725.90181900000005 TJ) x 1000000 kg/kt; valor aplicado 0.34291138757981265 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="75" customHeight="1">
       <x:c r="A93" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5656,13 +5893,13 @@
         <x:v>CRT1A|2018|1.A.4.b|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J93" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C30 (TJ), H30 (kt CO2)</x:v>
       </x:c>
       <x:c r="K93" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94">
+        <x:v>FE = (H30=31478.9951 kt CO2 / C30=281062.45600000001 TJ) x 1000000 kg/kt; valor aplicado 112000.00009962199 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="75" customHeight="1">
       <x:c r="A94" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5691,13 +5928,13 @@
         <x:v>CRT1A|2018|1.A.4.b|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J94" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C30 (TJ), I30 (kt CH4)</x:v>
       </x:c>
       <x:c r="K94" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95">
+        <x:v>FE = (I30=84.318736900000005 kt CH4 / C30=281062.45600000001 TJ) x 1000000 kg/kt; valor aplicado 300.00000035579285 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="75" customHeight="1">
       <x:c r="A95" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5726,13 +5963,13 @@
         <x:v>CRT1A|2018|1.A.4.b|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J95" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C30 (TJ), J30 (kt N2O)</x:v>
       </x:c>
       <x:c r="K95" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96">
+        <x:v>FE = (J30=1.12424982 kt N2O / C30=281062.45600000001 TJ) x 1000000 kg/kt; valor aplicado 3.9999999857682877 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="75" customHeight="1">
       <x:c r="A96" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5761,13 +5998,13 @@
         <x:v>CRT1A|2018|1.A.4.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J96" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C25 (TJ), H25 (kt CO2)</x:v>
       </x:c>
       <x:c r="K96" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97">
+        <x:v>FE = (H25=908.16433700000005 kt CO2 / C25=14389.5772 TJ) x 1000000 kg/kt; valor aplicado 63112.64913329073 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="75" customHeight="1">
       <x:c r="A97" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5796,13 +6033,13 @@
         <x:v>CRT1A|2018|1.A.4.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J97" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C25 (TJ), I25 (kt CH4)</x:v>
       </x:c>
       <x:c r="K97" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98">
+        <x:v>FE = (I25=0.072051299999999999 kt CH4 / C25=14389.5772 TJ) x 1000000 kg/kt; valor aplicado 5.007186729572569 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="75" customHeight="1">
       <x:c r="A98" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -5831,10 +6068,10 @@
         <x:v>CRT1A|2018|1.A.4.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J98" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2018|1.A.4.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.A(a)s4!C25 (TJ), J25 (kt N2O)</x:v>
       </x:c>
       <x:c r="K98" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J25=0.0014492999999999999 kt N2O / C25=14389.5772 TJ) x 1000000 kg/kt; valor aplicado 0.10071873411263257 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -6887,7 +7124,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_NO|2018|1.B.2.b.ii|NO|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
+    <x:row r="129" ht="87" customHeight="1">
       <x:c r="A129" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -6916,13 +7153,13 @@
         <x:v>CRT1B2|2018|1.B.2.a.ii|CO2</x:v>
       </x:c>
       <x:c r="J129" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2018|1.B.2.a.ii|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.B.2!I12 (kt CO2); denominador PSUT BEV2_00099</x:v>
       </x:c>
       <x:c r="K129" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130">
+        <x:v>FE = (I12=0.00013359498 kt CO2 / extracción PSUT BEV2_00099=19402.7855 TJ) x 1000000 kg/kt; valor aplicado 0.006885350559588466 kg CO2/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="87" customHeight="1">
       <x:c r="A130" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -6951,13 +7188,13 @@
         <x:v>CRT1B2|2018|1.B.2.a.ii|CH4</x:v>
       </x:c>
       <x:c r="J130" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2018|1.B.2.a.ii|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.B.2!J12 (kt CH4); denominador PSUT BEV2_00099</x:v>
       </x:c>
       <x:c r="K130" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131">
+        <x:v>FE = (J12=0.0018330474 kt CH4 / extracción PSUT BEV2_00099=19402.7855 TJ) x 1000000 kg/kt; valor aplicado 0.0944734146548185 kg CH4/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="75" customHeight="1">
       <x:c r="A131" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -6977,7 +7214,7 @@
         <x:v>N2O</x:v>
       </x:c>
       <x:c r="G131" s="73" t="str">
-        <x:v>observacion_externa</x:v>
+        <x:v>clave_no_sin_valor_numerico</x:v>
       </x:c>
       <x:c r="H131" s="73" t="str">
         <x:v>UNFCCC_GTM_CRT_2024</x:v>
@@ -6986,13 +7223,13 @@
         <x:v>CRT1B2|2018|1.B.2.a.ii|N2O</x:v>
       </x:c>
       <x:c r="J131" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2018|1.B.2.a.ii|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2018.xlsx; Table1.B.2!K12 (kt N2O); denominador PSUT BEV2_00099</x:v>
       </x:c>
       <x:c r="K131" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132">
+        <x:v>La celda K12 de emisiones N2O y H12 del factor fuente están vacías. NO es la notación interna conservada por el modelo para ausencia numérica; no se transcribió un NO literal de K12 y no representa una emisión igual a cero. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2018.xlsx; SHA-256 1efce35f9670e4cbbd297ded271efaf4a32192bfcc9aa0eba7acb87b01dddc8d.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="75" customHeight="1">
       <x:c r="A132" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7021,13 +7258,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J132" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C37 (TJ), H37 (kt CO2)</x:v>
       </x:c>
       <x:c r="K132" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133">
+        <x:v>FE = (H37=5233.407451 kt CO2 / C37=52473.657590000003 TJ) x 1000000 kg/kt; valor aplicado 99733.99399544316 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="75" customHeight="1">
       <x:c r="A133" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7056,13 +7293,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J133" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C37 (TJ), I37 (kt CH4)</x:v>
       </x:c>
       <x:c r="K133" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134">
+        <x:v>FE = (I37=1.565293628 kt CH4 / C37=52473.657590000003 TJ) x 1000000 kg/kt; valor aplicado 29.83008427257605 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="75" customHeight="1">
       <x:c r="A134" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7091,13 +7328,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J134" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C37 (TJ), J37 (kt N2O)</x:v>
       </x:c>
       <x:c r="K134" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135">
+        <x:v>FE = (J37=0.208695569 kt N2O / C37=52473.657590000003 TJ) x 1000000 kg/kt; valor aplicado 3.9771492704135696 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="75" customHeight="1">
       <x:c r="A135" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7126,13 +7363,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J135" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C33 (TJ), H33 (kt CO2)</x:v>
       </x:c>
       <x:c r="K135" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136">
+        <x:v>FE = (H33=4884.7605819999999 kt CO2 / C33=49692.376210000002 TJ) x 1000000 kg/kt; valor aplicado 98300.00001120895 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="75" customHeight="1">
       <x:c r="A136" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7161,13 +7398,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J136" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C33 (TJ), I33 (kt CH4)</x:v>
       </x:c>
       <x:c r="K136" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137">
+        <x:v>FE = (I33=0.049692376000000003 kt CH4 / C33=49692.376210000002 TJ) x 1000000 kg/kt; valor aplicado 0.9999999957739997 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="75" customHeight="1">
       <x:c r="A137" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7196,13 +7433,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J137" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C33 (TJ), J33 (kt N2O)</x:v>
       </x:c>
       <x:c r="K137" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138">
+        <x:v>FE = (J33=0.074538564000000002 kt N2O / C33=49692.376210000002 TJ) x 1000000 kg/kt; valor aplicado 1.4999999936609993 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="75" customHeight="1">
       <x:c r="A138" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7231,13 +7468,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J138" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C32 (TJ), H32 (kt CO2)</x:v>
       </x:c>
       <x:c r="K138" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139">
+        <x:v>FE = (H32=327.65971889999997 kt CO2 / C32=4237.9471409999996 TJ) x 1000000 kg/kt; valor aplicado 77315.66911962104 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="75" customHeight="1">
       <x:c r="A139" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7266,13 +7503,13 @@
         <x:v>CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J139" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C32 (TJ), I32 (kt CH4)</x:v>
       </x:c>
       <x:c r="K139" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140">
+        <x:v>FE = (I32=0.012713841 kt CH4 / C32=4237.9471409999996 TJ) x 1000000 kg/kt; valor aplicado 2.9999999001875235 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="75" customHeight="1">
       <x:c r="A140" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7301,10 +7538,10 @@
         <x:v>CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J140" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C32 (TJ), J32 (kt N2O)</x:v>
       </x:c>
       <x:c r="K140" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J32=0.0025427679999999999 kt N2O / C32=4237.9471409999996 TJ) x 1000000 kg/kt; valor aplicado 0.5999999328448444 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -7412,7 +7649,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_COMB|2019|1.A.1.a.i|GASEOUS_FUELS|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="144">
+    <x:row r="144" ht="75" customHeight="1">
       <x:c r="A144" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7441,13 +7678,13 @@
         <x:v>CRT1A|2019|1.A.1.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J144" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C39 (TJ), H39 (kt CO2)</x:v>
       </x:c>
       <x:c r="K144" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145">
+        <x:v>FE = (H39=0.54624026999999997 kt CO2 / C39=7.5120592400000001 TJ) x 1000000 kg/kt; valor aplicado 72715.11745959021 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="75" customHeight="1">
       <x:c r="A145" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7476,13 +7713,13 @@
         <x:v>CRT1A|2019|1.A.1.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J145" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C39 (TJ), I39 (kt CH4)</x:v>
       </x:c>
       <x:c r="K145" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146">
+        <x:v>FE = (I39=2.2535999999999999e-05 kt CH4 / C39=7.5120592400000001 TJ) x 1000000 kg/kt; valor aplicado 2.9999763420396026 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="75" customHeight="1">
       <x:c r="A146" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7511,13 +7748,13 @@
         <x:v>CRT1A|2019|1.A.1.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J146" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2019|1.A.1.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s1!C39 (TJ), J39 (kt N2O)</x:v>
       </x:c>
       <x:c r="K146" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147">
+        <x:v>FE = (J39=4.5071999999999998e-06 kt N2O / C39=7.5120592400000001 TJ) x 1000000 kg/kt; valor aplicado 0.5999952684079206 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="102" customHeight="1">
       <x:c r="A147" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7546,13 +7783,13 @@
         <x:v>CRT1A|2019|1.A.2|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J147" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2019|1.A.2|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s2!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K147" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148">
+        <x:v>FE = (H11=2716.6332299999999 kt CO2 / C11=32244.4136 TJ) x 1000000 kg/kt; valor aplicado 84251.28345332971 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="87" customHeight="1">
       <x:c r="A148" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7581,13 +7818,13 @@
         <x:v>CRT1A|2019|1.A.2|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J148" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2019|1.A.2|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s2!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K148" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149">
+        <x:v>FE = (I11=0.091232720000000003 kt CH4 / C11=32244.4136 TJ) x 1000000 kg/kt; valor aplicado 2.8294116659017177 kg CH4/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="87" customHeight="1">
       <x:c r="A149" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7616,13 +7853,13 @@
         <x:v>CRT1A|2019|1.A.2|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J149" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2019|1.A.2|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s2!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K149" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150">
+        <x:v>FE = (J11=0.017424410000000001 kt N2O / C11=32244.4136 TJ) x 1000000 kg/kt; valor aplicado 0.54038538942448 kg N2O/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="132" customHeight="1">
       <x:c r="A150" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7651,13 +7888,13 @@
         <x:v>CRT1A|2019|1.A.3|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J150" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2019|1.A.3|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s3!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K150" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151">
+        <x:v>FE = (H11=9615.9336513019989 kt CO2 / C11=138255.68783045001 TJ) x 1000000 kg/kt; valor aplicado 69551.81231382326 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="117" customHeight="1">
       <x:c r="A151" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7686,13 +7923,13 @@
         <x:v>CRT1A|2019|1.A.3|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J151" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2019|1.A.3|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s3!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K151" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152">
+        <x:v>FE = (I11=2.4062930982999995 kt CH4 / C11=138255.68783045001 TJ) x 1000000 kg/kt; valor aplicado 17.40465897685858 kg CH4/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="117" customHeight="1">
       <x:c r="A152" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7721,13 +7958,13 @@
         <x:v>CRT1A|2019|1.A.3|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J152" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2019|1.A.3|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s3!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K152" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153">
+        <x:v>FE = (J11=0.47660826799999995 kt N2O / C11=138255.68783045001 TJ) x 1000000 kg/kt; valor aplicado 3.4472959158431795 kg N2O/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="75" customHeight="1">
       <x:c r="A153" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7756,13 +7993,13 @@
         <x:v>CRT1A|2019|1.A.4.a|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J153" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C23 (TJ), H23 (kt CO2)</x:v>
       </x:c>
       <x:c r="K153" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154">
+        <x:v>FE = (H23=975.53091500000005 kt CO2 / C23=8710.0974600000009 TJ) x 1000000 kg/kt; valor aplicado 111999.99994029917 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="75" customHeight="1">
       <x:c r="A154" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7791,13 +8028,13 @@
         <x:v>CRT1A|2019|1.A.4.a|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J154" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C23 (TJ), I23 (kt CH4)</x:v>
       </x:c>
       <x:c r="K154" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155">
+        <x:v>FE = (I23=2.6130292399999999 kt CH4 / C23=8710.0974600000009 TJ) x 1000000 kg/kt; valor aplicado 300.0000002296185 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="75" customHeight="1">
       <x:c r="A155" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7826,13 +8063,13 @@
         <x:v>CRT1A|2019|1.A.4.a|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J155" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C23 (TJ), J23 (kt N2O)</x:v>
       </x:c>
       <x:c r="K155" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156">
+        <x:v>FE = (J23=0.034840389999999999 kt N2O / C23=8710.0974600000009 TJ) x 1000000 kg/kt; valor aplicado 4.000000018369484 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="75" customHeight="1">
       <x:c r="A156" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7861,13 +8098,13 @@
         <x:v>CRT1A|2019|1.A.4.a|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J156" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C18 (TJ), H18 (kt CO2)</x:v>
       </x:c>
       <x:c r="K156" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157">
+        <x:v>FE = (H18=47.656202499999999 kt CO2 / C18=721.800614 TJ) x 1000000 kg/kt; valor aplicado 66024.05370079112 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="75" customHeight="1">
       <x:c r="A157" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7896,13 +8133,13 @@
         <x:v>CRT1A|2019|1.A.4.a|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J157" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C18 (TJ), I18 (kt CH4)</x:v>
       </x:c>
       <x:c r="K157" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158">
+        <x:v>FE = (I18=0.00529577 kt CH4 / C18=721.800614 TJ) x 1000000 kg/kt; valor aplicado 7.336887635288158 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="75" customHeight="1">
       <x:c r="A158" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7931,13 +8168,13 @@
         <x:v>CRT1A|2019|1.A.4.a|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J158" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.a|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C18 (TJ), J18 (kt N2O)</x:v>
       </x:c>
       <x:c r="K158" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159">
+        <x:v>FE = (J18=0.00024085999999999999 kt N2O / C18=721.800614 TJ) x 1000000 kg/kt; valor aplicado 0.3336932600614274 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="75" customHeight="1">
       <x:c r="A159" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -7966,13 +8203,13 @@
         <x:v>CRT1A|2019|1.A.4.b|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J159" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C30 (TJ), H30 (kt CO2)</x:v>
       </x:c>
       <x:c r="K159" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160">
+        <x:v>FE = (H30=31542.166300000001 kt CO2 / C30=281626.484 TJ) x 1000000 kg/kt; valor aplicado 112000.00032667382 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="75" customHeight="1">
       <x:c r="A160" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -8001,13 +8238,13 @@
         <x:v>CRT1A|2019|1.A.4.b|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J160" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C30 (TJ), I30 (kt CH4)</x:v>
       </x:c>
       <x:c r="K160" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161">
+        <x:v>FE = (I30=84.487945300000007 kt CH4 / C30=281626.484 TJ) x 1000000 kg/kt; valor aplicado 300.00000035508026 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="75" customHeight="1">
       <x:c r="A161" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -8036,13 +8273,13 @@
         <x:v>CRT1A|2019|1.A.4.b|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J161" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C30 (TJ), J30 (kt N2O)</x:v>
       </x:c>
       <x:c r="K161" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162">
+        <x:v>FE = (J30=1.1265059399999999 kt N2O / C30=281626.484 TJ) x 1000000 kg/kt; valor aplicado 4.000000014203209 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="75" customHeight="1">
       <x:c r="A162" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -8071,13 +8308,13 @@
         <x:v>CRT1A|2019|1.A.4.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J162" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C25 (TJ), H25 (kt CO2)</x:v>
       </x:c>
       <x:c r="K162" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
+        <x:v>FE = (H25=944.99154499999997 kt CO2 / C25=14954.6947 TJ) x 1000000 kg/kt; valor aplicado 63190.29334647667 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="75" customHeight="1">
       <x:c r="A163" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -8106,13 +8343,13 @@
         <x:v>CRT1A|2019|1.A.4.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J163" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C25 (TJ), I25 (kt CH4)</x:v>
       </x:c>
       <x:c r="K163" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164">
+        <x:v>FE = (I25=0.075540700000000002 kt CH4 / C25=14954.6947 TJ) x 1000000 kg/kt; valor aplicado 5.051303387691358 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="75" customHeight="1">
       <x:c r="A164" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -8141,10 +8378,10 @@
         <x:v>CRT1A|2019|1.A.4.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J164" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2019|1.A.4.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.A(a)s4!C25 (TJ), J25 (kt N2O)</x:v>
       </x:c>
       <x:c r="K164" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J25=0.00157219 kt N2O / C25=14954.6947 TJ) x 1000000 kg/kt; valor aplicado 0.10513019700763267 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -9197,7 +9434,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_NO|2019|1.B.2.b.ii|NO|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="195">
+    <x:row r="195" ht="87" customHeight="1">
       <x:c r="A195" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9226,13 +9463,13 @@
         <x:v>CRT1B2|2019|1.B.2.a.ii|CO2</x:v>
       </x:c>
       <x:c r="J195" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2019|1.B.2.a.ii|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.B.2!I12 (kt CO2); denominador PSUT BEV2_00337</x:v>
       </x:c>
       <x:c r="K195" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196">
+        <x:v>FE = (I12=0.00013679 kt CO2 / extracción PSUT BEV2_00337=20207.7029 TJ) x 1000000 kg/kt; valor aplicado 0.0067692008674573294 kg CO2/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="87" customHeight="1">
       <x:c r="A196" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9261,13 +9498,13 @@
         <x:v>CRT1B2|2019|1.B.2.a.ii|CH4</x:v>
       </x:c>
       <x:c r="J196" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2019|1.B.2.a.ii|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.B.2!J12 (kt CH4); denominador PSUT BEV2_00337</x:v>
       </x:c>
       <x:c r="K196" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197">
+        <x:v>FE = (J12=0.00187684 kt CH4 / extracción PSUT BEV2_00337=20207.7029 TJ) x 1000000 kg/kt; valor aplicado 0.09287745417120123 kg CH4/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="75" customHeight="1">
       <x:c r="A197" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9287,7 +9524,7 @@
         <x:v>N2O</x:v>
       </x:c>
       <x:c r="G197" s="73" t="str">
-        <x:v>observacion_externa</x:v>
+        <x:v>clave_no_sin_valor_numerico</x:v>
       </x:c>
       <x:c r="H197" s="73" t="str">
         <x:v>UNFCCC_GTM_CRT_2024</x:v>
@@ -9296,13 +9533,13 @@
         <x:v>CRT1B2|2019|1.B.2.a.ii|N2O</x:v>
       </x:c>
       <x:c r="J197" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2019|1.B.2.a.ii|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2019.xlsx; Table1.B.2!K12 (kt N2O); denominador PSUT BEV2_00337</x:v>
       </x:c>
       <x:c r="K197" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198">
+        <x:v>La celda K12 de emisiones N2O y H12 del factor fuente están vacías. NO es la notación interna conservada por el modelo para ausencia numérica; no se transcribió un NO literal de K12 y no representa una emisión igual a cero. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2019.xlsx; SHA-256 67d581bfd7a3e19c8ef8912e47014d2b2594b633567b44db6a66a46d21778680.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="75" customHeight="1">
       <x:c r="A198" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9331,13 +9568,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J198" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C37 (TJ), H37 (kt CO2)</x:v>
       </x:c>
       <x:c r="K198" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199">
+        <x:v>FE = (H37=5258.6748509999998 kt CO2 / C37=52714.112209999999 TJ) x 1000000 kg/kt; valor aplicado 99758.387849742 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="75" customHeight="1">
       <x:c r="A199" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9366,13 +9603,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J199" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C37 (TJ), I37 (kt CH4)</x:v>
       </x:c>
       <x:c r="K199" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200">
+        <x:v>FE = (I37=1.5732877999999999 kt CH4 / C37=52714.112209999999 TJ) x 1000000 kg/kt; valor aplicado 29.84566625598113 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="75" customHeight="1">
       <x:c r="A200" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9401,13 +9638,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J200" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C37 (TJ), J37 (kt N2O)</x:v>
       </x:c>
       <x:c r="K200" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201">
+        <x:v>FE = (J37=0.20976235500000001 kt N2O / C37=52714.112209999999 TJ) x 1000000 kg/kt; valor aplicado 3.979244763989548 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="75" customHeight="1">
       <x:c r="A201" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9436,13 +9673,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J201" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C33 (TJ), H33 (kt CO2)</x:v>
       </x:c>
       <x:c r="K201" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202">
+        <x:v>FE = (H33=3153.910488 kt CO2 / C33=32084.542089999999 TJ) x 1000000 kg/kt; valor aplicado 98300.00001723571 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="75" customHeight="1">
       <x:c r="A202" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9471,13 +9708,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J202" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C33 (TJ), I33 (kt CH4)</x:v>
       </x:c>
       <x:c r="K202" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203">
+        <x:v>FE = (I33=0.032084542000000001 kt CH4 / C33=32084.542089999999 TJ) x 1000000 kg/kt; valor aplicado 0.999999997194911 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="75" customHeight="1">
       <x:c r="A203" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9506,13 +9743,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J203" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C33 (TJ), J33 (kt N2O)</x:v>
       </x:c>
       <x:c r="K203" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204">
+        <x:v>FE = (J33=0.048126812999999997 kt N2O / C33=32084.542089999999 TJ) x 1000000 kg/kt; valor aplicado 1.4999999957923662 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="75" customHeight="1">
       <x:c r="A204" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9541,13 +9778,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J204" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C32 (TJ), H32 (kt CO2)</x:v>
       </x:c>
       <x:c r="K204" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205">
+        <x:v>FE = (H32=263.5400199 kt CO2 / C32=3410.059315 TJ) x 1000000 kg/kt; valor aplicado 77283.11901812184 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="75" customHeight="1">
       <x:c r="A205" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9576,13 +9813,13 @@
         <x:v>CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J205" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C32 (TJ), I32 (kt CH4)</x:v>
       </x:c>
       <x:c r="K205" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206">
+        <x:v>FE = (I32=0.010230177999999999 kt CH4 / C32=3410.059315 TJ) x 1000000 kg/kt; valor aplicado 3.0000000161287517 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="75" customHeight="1">
       <x:c r="A206" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9611,10 +9848,10 @@
         <x:v>CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J206" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C32 (TJ), J32 (kt N2O)</x:v>
       </x:c>
       <x:c r="K206" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J32=0.0020460360000000002 kt N2O / C32=3410.059315 TJ) x 1000000 kg/kt; valor aplicado 0.6000001205257629 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -9722,7 +9959,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_COMB|2020|1.A.1.a.i|GASEOUS_FUELS|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="210">
+    <x:row r="210" ht="75" customHeight="1">
       <x:c r="A210" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9751,13 +9988,13 @@
         <x:v>CRT1A|2020|1.A.1.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J210" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C39 (TJ), H39 (kt CO2)</x:v>
       </x:c>
       <x:c r="K210" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211">
+        <x:v>FE = (H39=0.15961942000000001 kt CO2 / C39=2.18344286 TJ) x 1000000 kg/kt; valor aplicado 73104.46402064308 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="75" customHeight="1">
       <x:c r="A211" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9786,13 +10023,13 @@
         <x:v>CRT1A|2020|1.A.1.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J211" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C39 (TJ), I39 (kt CH4)</x:v>
       </x:c>
       <x:c r="K211" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212">
+        <x:v>FE = (I39=6.5502999999999998e-06 kt CH4 / C39=2.18344286 TJ) x 1000000 kg/kt; valor aplicado 2.999986910580293 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="75" customHeight="1">
       <x:c r="A212" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9821,13 +10058,13 @@
         <x:v>CRT1A|2020|1.A.1.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J212" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2020|1.A.1.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s1!C39 (TJ), J39 (kt N2O)</x:v>
       </x:c>
       <x:c r="K212" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213">
+        <x:v>FE = (J39=1.3101e-06 kt N2O / C39=2.18344286 TJ) x 1000000 kg/kt; valor aplicado 0.6000157018077404 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="102" customHeight="1">
       <x:c r="A213" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9856,13 +10093,13 @@
         <x:v>CRT1A|2020|1.A.2|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J213" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2020|1.A.2|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s2!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K213" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214">
+        <x:v>FE = (H11=2819.3963800000001 kt CO2 / C11=33182.650900000001 TJ) x 1000000 kg/kt; valor aplicado 84965.97780860239 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="87" customHeight="1">
       <x:c r="A214" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9891,13 +10128,13 @@
         <x:v>CRT1A|2020|1.A.2|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J214" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2020|1.A.2|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s2!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K214" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215">
+        <x:v>FE = (I11=0.093332159999999997 kt CH4 / C11=33182.650900000001 TJ) x 1000000 kg/kt; valor aplicado 2.812679441472833 kg CH4/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="87" customHeight="1">
       <x:c r="A215" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9926,13 +10163,13 @@
         <x:v>CRT1A|2020|1.A.2|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J215" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2020|1.A.2|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s2!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K215" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216">
+        <x:v>FE = (J11=0.01796155 kt N2O / C11=33182.650900000001 TJ) x 1000000 kg/kt; valor aplicado 0.5412934022097674 kg N2O/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="132" customHeight="1">
       <x:c r="A216" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9961,13 +10198,13 @@
         <x:v>CRT1A|2020|1.A.3|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J216" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2020|1.A.3|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s3!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K216" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217">
+        <x:v>FE = (H11=9536.1576406160002 kt CO2 / C11=135257.96384909001 TJ) x 1000000 kg/kt; valor aplicado 70503.48363409995 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="117" customHeight="1">
       <x:c r="A217" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -9996,13 +10233,13 @@
         <x:v>CRT1A|2020|1.A.3|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J217" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2020|1.A.3|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s3!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K217" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218">
+        <x:v>FE = (I11=2.5451499709999998 kt CH4 / C11=135257.96384909001 TJ) x 1000000 kg/kt; valor aplicado 18.817006397047898 kg CH4/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="117" customHeight="1">
       <x:c r="A218" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10031,13 +10268,13 @@
         <x:v>CRT1A|2020|1.A.3|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J218" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2020|1.A.3|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s3!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K218" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219">
+        <x:v>FE = (J11=0.470233805 kt N2O / C11=135257.96384909001 TJ) x 1000000 kg/kt; valor aplicado 3.4765701894244776 kg N2O/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="75" customHeight="1">
       <x:c r="A219" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10066,13 +10303,13 @@
         <x:v>CRT1A|2020|1.A.4.a|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J219" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C23 (TJ), H23 (kt CO2)</x:v>
       </x:c>
       <x:c r="K219" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220">
+        <x:v>FE = (H23=1004.93873 kt CO2 / C23=8972.6672099999996 TJ) x 1000000 kg/kt; valor aplicado 112000.00027639496 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="75" customHeight="1">
       <x:c r="A220" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10101,13 +10338,13 @@
         <x:v>CRT1A|2020|1.A.4.a|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J220" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C23 (TJ), I23 (kt CH4)</x:v>
       </x:c>
       <x:c r="K220" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221">
+        <x:v>FE = (I23=2.6918001600000001 kt CH4 / C23=8972.6672099999996 TJ) x 1000000 kg/kt; valor aplicado 299.9999996656513 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="75" customHeight="1">
       <x:c r="A221" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10136,13 +10373,13 @@
         <x:v>CRT1A|2020|1.A.4.a|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J221" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C23 (TJ), J23 (kt N2O)</x:v>
       </x:c>
       <x:c r="K221" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222">
+        <x:v>FE = (J23=0.03589067 kt N2O / C23=8972.6672099999996 TJ) x 1000000 kg/kt; valor aplicado 4.0000001292815135 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="75" customHeight="1">
       <x:c r="A222" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10171,13 +10408,13 @@
         <x:v>CRT1A|2020|1.A.4.a|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J222" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C18 (TJ), H18 (kt CO2)</x:v>
       </x:c>
       <x:c r="K222" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223">
+        <x:v>FE = (H18=49.237809200000001 kt CO2 / C18=745.332404 TJ) x 1000000 kg/kt; valor aplicado 66061.5437296887 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="75" customHeight="1">
       <x:c r="A223" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10206,13 +10443,13 @@
         <x:v>CRT1A|2020|1.A.4.a|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J223" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C18 (TJ), I18 (kt CH4)</x:v>
       </x:c>
       <x:c r="K223" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224">
+        <x:v>FE = (I18=0.0055052800000000004 kt CH4 / C18=745.332404 TJ) x 1000000 kg/kt; valor aplicado 7.386341946834235 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="75" customHeight="1">
       <x:c r="A224" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10241,13 +10478,13 @@
         <x:v>CRT1A|2020|1.A.4.a|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J224" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.a|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C18 (TJ), J18 (kt N2O)</x:v>
       </x:c>
       <x:c r="K224" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225">
+        <x:v>FE = (J18=0.00025240000000000001 kt N2O / C18=745.332404 TJ) x 1000000 kg/kt; valor aplicado 0.33864085157902246 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="75" customHeight="1">
       <x:c r="A225" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10276,13 +10513,13 @@
         <x:v>CRT1A|2020|1.A.4.b|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J225" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C30 (TJ), H30 (kt CO2)</x:v>
       </x:c>
       <x:c r="K225" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226">
+        <x:v>FE = (H30=32493.018899999999 kt CO2 / C30=290116.23999999999 TJ) x 1000000 kg/kt; valor aplicado 112000.00006893788 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="75" customHeight="1">
       <x:c r="A226" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10311,13 +10548,13 @@
         <x:v>CRT1A|2020|1.A.4.b|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J226" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C30 (TJ), I30 (kt CH4)</x:v>
       </x:c>
       <x:c r="K226" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227">
+        <x:v>FE = (I30=87.034871899999999 kt CH4 / C30=290116.23999999999 TJ) x 1000000 kg/kt; valor aplicado 299.9999996553106 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="75" customHeight="1">
       <x:c r="A227" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10346,13 +10583,13 @@
         <x:v>CRT1A|2020|1.A.4.b|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J227" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C30 (TJ), J30 (kt N2O)</x:v>
       </x:c>
       <x:c r="K227" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="228">
+        <x:v>FE = (J30=1.1604649600000001 kt N2O / C30=290116.23999999999 TJ) x 1000000 kg/kt; valor aplicado 4.000000000000001 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="75" customHeight="1">
       <x:c r="A228" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10381,13 +10618,13 @@
         <x:v>CRT1A|2020|1.A.4.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J228" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C25 (TJ), H25 (kt CO2)</x:v>
       </x:c>
       <x:c r="K228" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229">
+        <x:v>FE = (H25=947.56735900000001 kt CO2 / C25=15014.8359 TJ) x 1000000 kg/kt; valor aplicado 63108.73893733331 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="75" customHeight="1">
       <x:c r="A229" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10416,13 +10653,13 @@
         <x:v>CRT1A|2020|1.A.4.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J229" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C25 (TJ), I25 (kt CH4)</x:v>
       </x:c>
       <x:c r="K229" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230">
+        <x:v>FE = (I25=0.075148729999999997 kt CH4 / C25=15014.8359 TJ) x 1000000 kg/kt; valor aplicado 5.004965122529244 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="75" customHeight="1">
       <x:c r="A230" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -10451,10 +10688,10 @@
         <x:v>CRT1A|2020|1.A.4.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J230" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2020|1.A.4.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.A(a)s4!C25 (TJ), J25 (kt N2O)</x:v>
       </x:c>
       <x:c r="K230" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J25=0.0015089400000000001 kt N2O / C25=15014.8359 TJ) x 1000000 kg/kt; valor aplicado 0.10049660283000496 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -11507,7 +11744,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_NO|2020|1.B.2.b.ii|NO|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="261">
+    <x:row r="261" ht="87" customHeight="1">
       <x:c r="A261" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11536,13 +11773,13 @@
         <x:v>CRT1B2|2020|1.B.2.a.ii|CO2</x:v>
       </x:c>
       <x:c r="J261" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2020|1.B.2.a.ii|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.B.2!I12 (kt CO2); denominador PSUT BEV2_00589</x:v>
       </x:c>
       <x:c r="K261" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="262">
+        <x:v>FE = (I12=0.00011138 kt CO2 / extracción PSUT BEV2_00589=16453.6876 TJ) x 1000000 kg/kt; valor aplicado 0.006769303192556056 kg CO2/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="87" customHeight="1">
       <x:c r="A262" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11571,13 +11808,13 @@
         <x:v>CRT1B2|2020|1.B.2.a.ii|CH4</x:v>
       </x:c>
       <x:c r="J262" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2020|1.B.2.a.ii|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.B.2!J12 (kt CH4); denominador PSUT BEV2_00589</x:v>
       </x:c>
       <x:c r="K262" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="263">
+        <x:v>FE = (J12=0.00152818 kt CH4 / extracción PSUT BEV2_00589=16453.6876 TJ) x 1000000 kg/kt; valor aplicado 0.09287765983839391 kg CH4/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="75" customHeight="1">
       <x:c r="A263" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11597,7 +11834,7 @@
         <x:v>N2O</x:v>
       </x:c>
       <x:c r="G263" s="73" t="str">
-        <x:v>observacion_externa</x:v>
+        <x:v>clave_no_sin_valor_numerico</x:v>
       </x:c>
       <x:c r="H263" s="73" t="str">
         <x:v>UNFCCC_GTM_CRT_2024</x:v>
@@ -11606,13 +11843,13 @@
         <x:v>CRT1B2|2020|1.B.2.a.ii|N2O</x:v>
       </x:c>
       <x:c r="J263" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2020|1.B.2.a.ii|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2020.xlsx; Table1.B.2!K12 (kt N2O); denominador PSUT BEV2_00589</x:v>
       </x:c>
       <x:c r="K263" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="264">
+        <x:v>La celda K12 de emisiones N2O y H12 del factor fuente están vacías. NO es la notación interna conservada por el modelo para ausencia numérica; no se transcribió un NO literal de K12 y no representa una emisión igual a cero. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2020.xlsx; SHA-256 17f0e83d5b434cddc5e179c71e4106c1a96b35972ea36e19202a07e0219ebc6c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="75" customHeight="1">
       <x:c r="A264" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11641,13 +11878,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J264" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C37 (TJ), H37 (kt CO2)</x:v>
       </x:c>
       <x:c r="K264" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="265">
+        <x:v>FE = (H37=8574.5342170000004 kt CO2 / C37=85958.990359999996 TJ) x 1000000 kg/kt; valor aplicado 99751.45335106284 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="75" customHeight="1">
       <x:c r="A265" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11676,13 +11913,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J265" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C37 (TJ), I37 (kt CH4)</x:v>
       </x:c>
       <x:c r="K265" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266">
+        <x:v>FE = (I37=2.5651225800000002 kt CH4 / C37=85958.990359999996 TJ) x 1000000 kg/kt; valor aplicado 29.84123672529371 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="75" customHeight="1">
       <x:c r="A266" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11711,13 +11948,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J266" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C37 (TJ), J37 (kt N2O)</x:v>
       </x:c>
       <x:c r="K266" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="267">
+        <x:v>FE = (J37=0.34200065800000001 kt N2O / C37=85958.990359999996 TJ) x 1000000 kg/kt; valor aplicado 3.9786490810057953 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="75" customHeight="1">
       <x:c r="A267" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11746,13 +11983,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J267" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C33 (TJ), H33 (kt CO2)</x:v>
       </x:c>
       <x:c r="K267" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268">
+        <x:v>FE = (H33=4037.4213530000002 kt CO2 / C33=41072.445099999997 TJ) x 1000000 kg/kt; valor aplicado 98299.99999196542 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="75" customHeight="1">
       <x:c r="A268" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11781,13 +12018,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J268" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C33 (TJ), I33 (kt CH4)</x:v>
       </x:c>
       <x:c r="K268" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269">
+        <x:v>FE = (I33=0.041072444999999999 kt CH4 / C33=41072.445099999997 TJ) x 1000000 kg/kt; valor aplicado 0.9999999975652777 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="75" customHeight="1">
       <x:c r="A269" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11816,13 +12053,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J269" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C33 (TJ), J33 (kt N2O)</x:v>
       </x:c>
       <x:c r="K269" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270">
+        <x:v>FE = (J33=0.061608667999999998 kt N2O / C33=41072.445099999997 TJ) x 1000000 kg/kt; valor aplicado 1.5000000085215284 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="75" customHeight="1">
       <x:c r="A270" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11851,13 +12088,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J270" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C32 (TJ), H32 (kt CO2)</x:v>
       </x:c>
       <x:c r="K270" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="271">
+        <x:v>FE = (H32=186.9792597 kt CO2 / C32=2417.7554209999998 TJ) x 1000000 kg/kt; valor aplicado 77335.88686264392 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="75" customHeight="1">
       <x:c r="A271" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11886,13 +12123,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J271" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C32 (TJ), I32 (kt CH4)</x:v>
       </x:c>
       <x:c r="K271" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272">
+        <x:v>FE = (I32=0.0072532660000000004 kt CH4 / C32=2417.7554209999998 TJ) x 1000000 kg/kt; valor aplicado 2.999999891221421 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="75" customHeight="1">
       <x:c r="A272" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11921,13 +12158,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J272" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C32 (TJ), J32 (kt N2O)</x:v>
       </x:c>
       <x:c r="K272" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="273">
+        <x:v>FE = (J32=0.0014506530000000001 kt N2O / C32=2417.7554209999998 TJ) x 1000000 kg/kt; valor aplicado 0.599999895522931 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="75" customHeight="1">
       <x:c r="A273" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11956,13 +12193,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J273" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C34 (TJ), H34 (kt CO2)</x:v>
       </x:c>
       <x:c r="K273" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="274">
+        <x:v>FE = (H34=2.7589539159999998 kt CO2 / C34=49.179214190000003 TJ) x 1000000 kg/kt; valor aplicado 56099.9999988003 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="75" customHeight="1">
       <x:c r="A274" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -11991,13 +12228,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J274" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C34 (TJ), I34 (kt CH4)</x:v>
       </x:c>
       <x:c r="K274" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="275">
+        <x:v>FE = (I34=4.9179199999999998e-05 kt CH4 / C34=49.179214190000003 TJ) x 1000000 kg/kt; valor aplicado 0.9999997114634661 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="75" customHeight="1">
       <x:c r="A275" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12026,13 +12263,13 @@
         <x:v>CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J275" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.a.i|GASEOUS_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C34 (TJ), J34 (kt N2O)</x:v>
       </x:c>
       <x:c r="K275" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="276">
+        <x:v>FE = (J34=4.9179199999999997e-06 kt N2O / C34=49.179214190000003 TJ) x 1000000 kg/kt; valor aplicado 0.0999999711463466 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="75" customHeight="1">
       <x:c r="A276" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12061,13 +12298,13 @@
         <x:v>CRT1A|2021|1.A.1.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J276" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C39 (TJ), H39 (kt CO2)</x:v>
       </x:c>
       <x:c r="K276" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="277">
+        <x:v>FE = (H39=0.40462533000000001 kt CO2 / C39=5.5201273300000002 TJ) x 1000000 kg/kt; valor aplicado 73299.99940418042 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="75" customHeight="1">
       <x:c r="A277" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12096,13 +12333,13 @@
         <x:v>CRT1A|2021|1.A.1.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J277" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C39 (TJ), I39 (kt CH4)</x:v>
       </x:c>
       <x:c r="K277" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="278">
+        <x:v>FE = (I39=1.6560000000000001e-05 kt CH4 / C39=5.5201273300000002 TJ) x 1000000 kg/kt; valor aplicado 2.9999308005092704 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="75" customHeight="1">
       <x:c r="A278" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12131,13 +12368,13 @@
         <x:v>CRT1A|2021|1.A.1.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J278" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2021|1.A.1.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s1!C39 (TJ), J39 (kt N2O)</x:v>
       </x:c>
       <x:c r="K278" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="279">
+        <x:v>FE = (J39=3.3121e-06 kt N2O / C39=5.5201273300000002 TJ) x 1000000 kg/kt; valor aplicado 0.6000042756260117 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="102" customHeight="1">
       <x:c r="A279" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12166,13 +12403,13 @@
         <x:v>CRT1A|2021|1.A.2|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J279" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2021|1.A.2|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s2!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K279" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="280">
+        <x:v>FE = (H11=2937.3827299999998 kt CO2 / C11=35258.511400000003 TJ) x 1000000 kg/kt; valor aplicado 83309.89067224205 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="87" customHeight="1">
       <x:c r="A280" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12201,13 +12438,13 @@
         <x:v>CRT1A|2021|1.A.2|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J280" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2021|1.A.2|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s2!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K280" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="281">
+        <x:v>FE = (I11=0.098466949999999998 kt CH4 / C11=35258.511400000003 TJ) x 1000000 kg/kt; valor aplicado 2.7927143288301157 kg CH4/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="87" customHeight="1">
       <x:c r="A281" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12236,13 +12473,13 @@
         <x:v>CRT1A|2021|1.A.2|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J281" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2021|1.A.2|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s2!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K281" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="282">
+        <x:v>FE = (J11=0.018912180000000001 kt N2O / C11=35258.511400000003 TJ) x 1000000 kg/kt; valor aplicado 0.5363862298508723 kg N2O/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="132" customHeight="1">
       <x:c r="A282" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12271,13 +12508,13 @@
         <x:v>CRT1A|2021|1.A.3|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J282" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2021|1.A.3|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s3!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K282" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="283">
+        <x:v>FE = (H11=11348.10277883 kt CO2 / C11=161881.43589920001 TJ) x 1000000 kg/kt; valor aplicado 70101.3227106301 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="117" customHeight="1">
       <x:c r="A283" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12306,13 +12543,13 @@
         <x:v>CRT1A|2021|1.A.3|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J283" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2021|1.A.3|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s3!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K283" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284">
+        <x:v>FE = (I11=2.9856731990000003 kt CH4 / C11=161881.43589920001 TJ) x 1000000 kg/kt; valor aplicado 18.44357991029381 kg CH4/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="117" customHeight="1">
       <x:c r="A284" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12341,13 +12578,13 @@
         <x:v>CRT1A|2021|1.A.3|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J284" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2021|1.A.3|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s3!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K284" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="285">
+        <x:v>FE = (J11=0.560253008 kt N2O / C11=161881.43589920001 TJ) x 1000000 kg/kt; valor aplicado 3.4608848438239526 kg N2O/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="75" customHeight="1">
       <x:c r="A285" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12376,13 +12613,13 @@
         <x:v>CRT1A|2021|1.A.4.a|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J285" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C23 (TJ), H23 (kt CO2)</x:v>
       </x:c>
       <x:c r="K285" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="286">
+        <x:v>FE = (H23=1035.23305 kt CO2 / C23=9243.1522499999992 TJ) x 1000000 kg/kt; valor aplicado 111999.99978362363 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="75" customHeight="1">
       <x:c r="A286" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12411,13 +12648,13 @@
         <x:v>CRT1A|2021|1.A.4.a|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J286" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C23 (TJ), I23 (kt CH4)</x:v>
       </x:c>
       <x:c r="K286" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="287">
+        <x:v>FE = (I23=2.7729456699999999 kt CH4 / C23=9243.1522499999992 TJ) x 1000000 kg/kt; valor aplicado 299.99999945905904 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="75" customHeight="1">
       <x:c r="A287" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12446,13 +12683,13 @@
         <x:v>CRT1A|2021|1.A.4.a|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J287" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C23 (TJ), J23 (kt N2O)</x:v>
       </x:c>
       <x:c r="K287" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="288">
+        <x:v>FE = (J23=0.036972610000000003 kt N2O / C23=9243.1522499999992 TJ) x 1000000 kg/kt; valor aplicado 4.0000001081882 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="75" customHeight="1">
       <x:c r="A288" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12481,13 +12718,13 @@
         <x:v>CRT1A|2021|1.A.4.a|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J288" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C18 (TJ), H18 (kt CO2)</x:v>
       </x:c>
       <x:c r="K288" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="289">
+        <x:v>FE = (H18=57.066682399999998 kt CO2 / C18=863.60615199999995 TJ) x 1000000 kg/kt; valor aplicado 66079.52278691038 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="75" customHeight="1">
       <x:c r="A289" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12516,13 +12753,13 @@
         <x:v>CRT1A|2021|1.A.4.a|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J289" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C18 (TJ), I18 (kt CH4)</x:v>
       </x:c>
       <x:c r="K289" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="290">
+        <x:v>FE = (I18=0.0063931400000000003 kt CH4 / C18=863.60615199999995 TJ) x 1000000 kg/kt; valor aplicado 7.40284212333865 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="75" customHeight="1">
       <x:c r="A290" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12551,13 +12788,13 @@
         <x:v>CRT1A|2021|1.A.4.a|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J290" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.a|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C18 (TJ), J18 (kt N2O)</x:v>
       </x:c>
       <x:c r="K290" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="291">
+        <x:v>FE = (J18=0.00029387 kt N2O / C18=863.60615199999995 TJ) x 1000000 kg/kt; valor aplicado 0.34028243003993797 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="75" customHeight="1">
       <x:c r="A291" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12586,13 +12823,13 @@
         <x:v>CRT1A|2021|1.A.4.b|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J291" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C30 (TJ), H30 (kt CO2)</x:v>
       </x:c>
       <x:c r="K291" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="292">
+        <x:v>FE = (H30=33472.535300000003 kt CO2 / C30=298861.92300000001 TJ) x 1000000 kg/kt; valor aplicado 111999.99974570196 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="75" customHeight="1">
       <x:c r="A292" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12621,13 +12858,13 @@
         <x:v>CRT1A|2021|1.A.4.b|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J292" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C30 (TJ), I30 (kt CH4)</x:v>
       </x:c>
       <x:c r="K292" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="293">
+        <x:v>FE = (I30=89.658576800000006 kt CH4 / C30=298861.92300000001 TJ) x 1000000 kg/kt; valor aplicado 299.99999966539735 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="75" customHeight="1">
       <x:c r="A293" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12656,13 +12893,13 @@
         <x:v>CRT1A|2021|1.A.4.b|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J293" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C30 (TJ), J30 (kt N2O)</x:v>
       </x:c>
       <x:c r="K293" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="294">
+        <x:v>FE = (J30=1.19544769 kt N2O / C30=298861.92300000001 TJ) x 1000000 kg/kt; valor aplicado 3.999999993307946 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="75" customHeight="1">
       <x:c r="A294" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12691,13 +12928,13 @@
         <x:v>CRT1A|2021|1.A.4.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J294" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C25 (TJ), H25 (kt CO2)</x:v>
       </x:c>
       <x:c r="K294" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="295">
+        <x:v>FE = (H25=1089.7687699999999 kt CO2 / C25=17270.503499999999 TJ) x 1000000 kg/kt; valor aplicado 63099.999950783145 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="75" customHeight="1">
       <x:c r="A295" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12726,13 +12963,13 @@
         <x:v>CRT1A|2021|1.A.4.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J295" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C25 (TJ), I25 (kt CH4)</x:v>
       </x:c>
       <x:c r="K295" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="296">
+        <x:v>FE = (I25=0.086352520000000002 kt CH4 / C25=17270.503499999999 TJ) x 1000000 kg/kt; valor aplicado 5.00000014475548 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="75" customHeight="1">
       <x:c r="A296" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -12761,10 +12998,10 @@
         <x:v>CRT1A|2021|1.A.4.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J296" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2021|1.A.4.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.A(a)s4!C25 (TJ), J25 (kt N2O)</x:v>
       </x:c>
       <x:c r="K296" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J25=0.0017270499999999999 kt N2O / C25=17270.503499999999 TJ) x 1000000 kg/kt; valor aplicado 0.099999979734233 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -13817,7 +14054,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_NO|2021|1.B.2.b.ii|NO|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="327">
+    <x:row r="327" ht="87" customHeight="1">
       <x:c r="A327" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -13846,13 +14083,13 @@
         <x:v>CRT1B2|2021|1.B.2.a.ii|CO2</x:v>
       </x:c>
       <x:c r="J327" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2021|1.B.2.a.ii|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.B.2!I12 (kt CO2); denominador PSUT BEV2_00841</x:v>
       </x:c>
       <x:c r="K327" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="328">
+        <x:v>FE = (I12=0.000089894 kt CO2 / extracción PSUT BEV2_00841=13280.1494 TJ) x 1000000 kg/kt; valor aplicado 0.006769050354207612 kg CO2/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="87" customHeight="1">
       <x:c r="A328" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -13881,13 +14118,13 @@
         <x:v>CRT1B2|2021|1.B.2.a.ii|CH4</x:v>
       </x:c>
       <x:c r="J328" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2021|1.B.2.a.ii|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.B.2!J12 (kt CH4); denominador PSUT BEV2_00841</x:v>
       </x:c>
       <x:c r="K328" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="329">
+        <x:v>FE = (J12=0.00123343 kt CH4 / extracción PSUT BEV2_00841=13280.1494 TJ) x 1000000 kg/kt; valor aplicado 0.09287772018588887 kg CH4/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="75" customHeight="1">
       <x:c r="A329" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -13907,7 +14144,7 @@
         <x:v>N2O</x:v>
       </x:c>
       <x:c r="G329" s="73" t="str">
-        <x:v>observacion_externa</x:v>
+        <x:v>clave_no_sin_valor_numerico</x:v>
       </x:c>
       <x:c r="H329" s="73" t="str">
         <x:v>UNFCCC_GTM_CRT_2024</x:v>
@@ -13916,13 +14153,13 @@
         <x:v>CRT1B2|2021|1.B.2.a.ii|N2O</x:v>
       </x:c>
       <x:c r="J329" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2021|1.B.2.a.ii|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2021.xlsx; Table1.B.2!K12 (kt N2O); denominador PSUT BEV2_00841</x:v>
       </x:c>
       <x:c r="K329" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="330">
+        <x:v>La celda K12 de emisiones N2O y H12 del factor fuente están vacías. NO es la notación interna conservada por el modelo para ausencia numérica; no se transcribió un NO literal de K12 y no representa una emisión igual a cero. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2021.xlsx; SHA-256 72387c5108bf4044dc94c41679c64bff17814c9d1691106132a67186667b88ae.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="75" customHeight="1">
       <x:c r="A330" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -13951,13 +14188,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J330" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C37 (TJ), H37 (kt CO2)</x:v>
       </x:c>
       <x:c r="K330" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="331">
+        <x:v>FE = (H37=7353.7156830000004 kt CO2 / C37=73668.385750000001 TJ) x 1000000 kg/kt; valor aplicado 99821.86535151546 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="75" customHeight="1">
       <x:c r="A331" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -13986,13 +14223,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J331" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C37 (TJ), I37 (kt CH4)</x:v>
       </x:c>
       <x:c r="K331" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="332">
+        <x:v>FE = (I37=2.201669109 kt CH4 / C37=73668.385750000001 TJ) x 1000000 kg/kt; valor aplicado 29.886213558032253 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="75" customHeight="1">
       <x:c r="A332" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14021,13 +14258,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J332" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C37 (TJ), J37 (kt N2O)</x:v>
       </x:c>
       <x:c r="K332" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="333">
+        <x:v>FE = (J37=0.29354624600000001 kt N2O / C37=73668.385750000001 TJ) x 1000000 kg/kt; valor aplicado 3.9846976828863117 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="75" customHeight="1">
       <x:c r="A333" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14056,13 +14293,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J333" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|SOLID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C33 (TJ), H33 (kt CO2)</x:v>
       </x:c>
       <x:c r="K333" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="334">
+        <x:v>FE = (H33=1541.31826 kt CO2 / C33=15679.738149999999 TJ) x 1000000 kg/kt; valor aplicado 98299.9999907524 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="75" customHeight="1">
       <x:c r="A334" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14091,13 +14328,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J334" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|SOLID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C33 (TJ), I33 (kt CH4)</x:v>
       </x:c>
       <x:c r="K334" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="335">
+        <x:v>FE = (I33=0.015679737999999999 kt CH4 / C33=15679.738149999999 TJ) x 1000000 kg/kt; valor aplicado 0.9999999904335137 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="75" customHeight="1">
       <x:c r="A335" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14126,13 +14363,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J335" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|SOLID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C33 (TJ), J33 (kt N2O)</x:v>
       </x:c>
       <x:c r="K335" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="336">
+        <x:v>FE = (J33=0.023519607000000001 kt N2O / C33=15679.738149999999 TJ) x 1000000 kg/kt; valor aplicado 1.4999999856502706 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="75" customHeight="1">
       <x:c r="A336" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14161,13 +14398,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J336" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C32 (TJ), H32 (kt CO2)</x:v>
       </x:c>
       <x:c r="K336" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="337">
+        <x:v>FE = (H32=120.7754096 kt CO2 / C32=1564.667095 TJ) x 1000000 kg/kt; valor aplicado 77189.20528586945 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="75" customHeight="1">
       <x:c r="A337" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14196,13 +14433,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J337" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C32 (TJ), I32 (kt CH4)</x:v>
       </x:c>
       <x:c r="K337" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="338">
+        <x:v>FE = (I32=0.0046940009999999997 kt CH4 / C32=1564.667095 TJ) x 1000000 kg/kt; valor aplicado 2.9999998178526273 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="75" customHeight="1">
       <x:c r="A338" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14231,13 +14468,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J338" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C32 (TJ), J32 (kt N2O)</x:v>
       </x:c>
       <x:c r="K338" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="339">
+        <x:v>FE = (J32=0.00093880000000000005 kt N2O / C32=1564.667095 TJ) x 1000000 kg/kt; valor aplicado 0.5999998357478081 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="75" customHeight="1">
       <x:c r="A339" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14266,13 +14503,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J339" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C34 (TJ), H34 (kt CO2)</x:v>
       </x:c>
       <x:c r="K339" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="340">
+        <x:v>FE = (H34=2.3846468509999998 kt CO2 / C34=42.507073990000002 TJ) x 1000000 kg/kt; valor aplicado 56100.0000037876 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="75" customHeight="1">
       <x:c r="A340" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14301,13 +14538,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J340" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C34 (TJ), I34 (kt CH4)</x:v>
       </x:c>
       <x:c r="K340" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="341">
+        <x:v>FE = (I34=4.2507099999999998e-05 kt CH4 / C34=42.507073990000002 TJ) x 1000000 kg/kt; valor aplicado 1.0000006118981515 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" ht="75" customHeight="1">
       <x:c r="A341" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14336,13 +14573,13 @@
         <x:v>CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J341" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.a.i|GASEOUS_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C34 (TJ), J34 (kt N2O)</x:v>
       </x:c>
       <x:c r="K341" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="342">
+        <x:v>FE = (J34=4.2507099999999997e-06 kt N2O / C34=42.507073990000002 TJ) x 1000000 kg/kt; valor aplicado 0.10000006118981514 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="75" customHeight="1">
       <x:c r="A342" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14371,13 +14608,13 @@
         <x:v>CRT1A|2022|1.A.1.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J342" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C39 (TJ), H39 (kt CO2)</x:v>
       </x:c>
       <x:c r="K342" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="343">
+        <x:v>FE = (H39=1.735624209 kt CO2 / C39=24.02212068 TJ) x 1000000 kg/kt; valor aplicado 72251.08191405522 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="75" customHeight="1">
       <x:c r="A343" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14406,13 +14643,13 @@
         <x:v>CRT1A|2022|1.A.1.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J343" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C39 (TJ), I39 (kt CH4)</x:v>
       </x:c>
       <x:c r="K343" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="344">
+        <x:v>FE = (I39=7.2066399999999998e-05 kt CH4 / C39=24.02212068 TJ) x 1000000 kg/kt; valor aplicado 3.0000015802101947 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="75" customHeight="1">
       <x:c r="A344" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14441,13 +14678,13 @@
         <x:v>CRT1A|2022|1.A.1.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J344" s="73" t="str">
-        <x:v>Table1.A(a)s1; registro CRT1A|2022|1.A.1.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s1!C39 (TJ), J39 (kt N2O)</x:v>
       </x:c>
       <x:c r="K344" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="345">
+        <x:v>FE = (J39=1.44133e-05 kt N2O / C39=24.02212068 TJ) x 1000000 kg/kt; valor aplicado 0.6000011486080004 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="102" customHeight="1">
       <x:c r="A345" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14476,13 +14713,13 @@
         <x:v>CRT1A|2022|1.A.2|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J345" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2022|1.A.2|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s2!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K345" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="346">
+        <x:v>FE = (H11=4048.3265700000002 kt CO2 / C11=46880.033300000003 TJ) x 1000000 kg/kt; valor aplicado 86355.02761044327 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="87" customHeight="1">
       <x:c r="A346" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14511,13 +14748,13 @@
         <x:v>CRT1A|2022|1.A.2|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J346" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2022|1.A.2|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s2!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K346" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="347">
+        <x:v>FE = (I11=0.13341248999999999 kt CH4 / C11=46880.033300000003 TJ) x 1000000 kg/kt; valor aplicado 2.8458275433861515 kg CH4/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="87" customHeight="1">
       <x:c r="A347" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14546,13 +14783,13 @@
         <x:v>CRT1A|2022|1.A.2|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J347" s="73" t="str">
-        <x:v>Table1.A(a)s2; registro CRT1A|2022|1.A.2|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s2!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K347" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="348">
+        <x:v>FE = (J11=0.025757780000000001 kt N2O / C11=46880.033300000003 TJ) x 1000000 kg/kt; valor aplicado 0.5494403093779373 kg N2O/TJ. La fila fuente se denomina Liquid fuels y coincide con el total industrial; AGREGADO_FOSIL es la correspondencia interna del promedio, no un factor individual por producto. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="132" customHeight="1">
       <x:c r="A348" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14581,13 +14818,13 @@
         <x:v>CRT1A|2022|1.A.3|AGREGADO_FOSIL|CO2</x:v>
       </x:c>
       <x:c r="J348" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2022|1.A.3|AGREGADO_FOSIL|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s3!C11 (TJ), H11 (kt CO2)</x:v>
       </x:c>
       <x:c r="K348" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="349">
+        <x:v>FE = (H11=11066.67532389 kt CO2 / C11=159028.27216190001 TJ) x 1000000 kg/kt; valor aplicado 69589.3577503218 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="117" customHeight="1">
       <x:c r="A349" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14616,13 +14853,13 @@
         <x:v>CRT1A|2022|1.A.3|AGREGADO_FOSIL|CH4</x:v>
       </x:c>
       <x:c r="J349" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2022|1.A.3|AGREGADO_FOSIL|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s3!C11 (TJ), I11 (kt CH4)</x:v>
       </x:c>
       <x:c r="K349" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="350">
+        <x:v>FE = (I11=2.9318958230000001 kt CH4 / C11=159028.27216190001 TJ) x 1000000 kg/kt; valor aplicado 18.436318166213614 kg CH4/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="117" customHeight="1">
       <x:c r="A350" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14651,13 +14888,13 @@
         <x:v>CRT1A|2022|1.A.3|AGREGADO_FOSIL|N2O</x:v>
       </x:c>
       <x:c r="J350" s="73" t="str">
-        <x:v>Table1.A(a)s3; registro CRT1A|2022|1.A.3|AGREGADO_FOSIL|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s3!C11 (TJ), J11 (kt N2O)</x:v>
       </x:c>
       <x:c r="K350" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="351">
+        <x:v>FE = (J11=0.5459842949999999 kt N2O / C11=159028.27216190001 TJ) x 1000000 kg/kt; valor aplicado 3.4332530158169376 kg N2O/TJ. Promedio de transporte conservado. La CRT ofrece factores viales por producto en filas 21-23; no se sustituyen en esta corrección de trazabilidad. C18 (Jet kerosene) tiene actividad numérica y H18:J18 están vacías; la actividad forma parte de C10/C11. Esta limitación del promedio queda pendiente de decisión. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="75" customHeight="1">
       <x:c r="A351" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14686,13 +14923,13 @@
         <x:v>CRT1A|2022|1.A.4.a|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J351" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C23 (TJ), H23 (kt CO2)</x:v>
       </x:c>
       <x:c r="K351" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="352">
+        <x:v>FE = (H23=1066.4406100000001 kt CO2 / C23=9521.7911800000002 TJ) x 1000000 kg/kt; valor aplicado 111999.99977315193 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="75" customHeight="1">
       <x:c r="A352" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14721,13 +14958,13 @@
         <x:v>CRT1A|2022|1.A.4.a|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J352" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C23 (TJ), I23 (kt CH4)</x:v>
       </x:c>
       <x:c r="K352" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="353">
+        <x:v>FE = (I23=2.85653735 kt CH4 / C23=9521.7911800000002 TJ) x 1000000 kg/kt; valor aplicado 299.999999579911 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="75" customHeight="1">
       <x:c r="A353" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14756,13 +14993,13 @@
         <x:v>CRT1A|2022|1.A.4.a|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J353" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C23 (TJ), J23 (kt N2O)</x:v>
       </x:c>
       <x:c r="K353" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="354">
+        <x:v>FE = (J23=0.038087160000000002 kt N2O / C23=9521.7911800000002 TJ) x 1000000 kg/kt; valor aplicado 3.9999995042949474 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="75" customHeight="1">
       <x:c r="A354" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14791,13 +15028,13 @@
         <x:v>CRT1A|2022|1.A.4.a|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J354" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C18 (TJ), H18 (kt CO2)</x:v>
       </x:c>
       <x:c r="K354" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="355">
+        <x:v>FE = (H18=58.193158400000002 kt CO2 / C18=882.13929700000006 TJ) x 1000000 kg/kt; valor aplicado 65968.21907594941 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="75" customHeight="1">
       <x:c r="A355" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14826,13 +15063,13 @@
         <x:v>CRT1A|2022|1.A.4.a|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J355" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C18 (TJ), I18 (kt CH4)</x:v>
       </x:c>
       <x:c r="K355" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="356">
+        <x:v>FE = (I18=0.0064511600000000001 kt CH4 / C18=882.13929700000006 TJ) x 1000000 kg/kt; valor aplicado 7.3130853845183585 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="75" customHeight="1">
       <x:c r="A356" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14861,13 +15098,13 @@
         <x:v>CRT1A|2022|1.A.4.a|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J356" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.a|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C18 (TJ), J18 (kt N2O)</x:v>
       </x:c>
       <x:c r="K356" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="357">
+        <x:v>FE = (J18=0.00029226000000000002 kt N2O / C18=882.13929700000006 TJ) x 1000000 kg/kt; valor aplicado 0.3313082196813187 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="75" customHeight="1">
       <x:c r="A357" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14896,13 +15133,13 @@
         <x:v>CRT1A|2022|1.A.4.b|BIOMASS|CO2</x:v>
       </x:c>
       <x:c r="J357" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|BIOMASS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C30 (TJ), H30 (kt CO2)</x:v>
       </x:c>
       <x:c r="K357" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="358">
+        <x:v>FE = (H30=34481.5798 kt CO2 / C30=307871.24800000002 TJ) x 1000000 kg/kt; valor aplicado 112000.00007795465 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="75" customHeight="1">
       <x:c r="A358" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14931,13 +15168,13 @@
         <x:v>CRT1A|2022|1.A.4.b|BIOMASS|CH4</x:v>
       </x:c>
       <x:c r="J358" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|BIOMASS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C30 (TJ), I30 (kt CH4)</x:v>
       </x:c>
       <x:c r="K358" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="359">
+        <x:v>FE = (I30=92.361374400000003 kt CH4 / C30=307871.24800000002 TJ) x 1000000 kg/kt; valor aplicado 300.0 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="75" customHeight="1">
       <x:c r="A359" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -14966,13 +15203,13 @@
         <x:v>CRT1A|2022|1.A.4.b|BIOMASS|N2O</x:v>
       </x:c>
       <x:c r="J359" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|BIOMASS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C30 (TJ), J30 (kt N2O)</x:v>
       </x:c>
       <x:c r="K359" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="360">
+        <x:v>FE = (J30=1.23148499 kt N2O / C30=307871.24800000002 TJ) x 1000000 kg/kt; valor aplicado 3.9999999935037778 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="75" customHeight="1">
       <x:c r="A360" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -15001,13 +15238,13 @@
         <x:v>CRT1A|2022|1.A.4.b|LIQUID_FUELS|CO2</x:v>
       </x:c>
       <x:c r="J360" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|LIQUID_FUELS|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C25 (TJ), H25 (kt CO2)</x:v>
       </x:c>
       <x:c r="K360" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="361">
+        <x:v>FE = (H25=1151.62745 kt CO2 / C25=18250.831200000001 TJ) x 1000000 kg/kt; valor aplicado 63100.000070133785 kg CO2/TJ. La columna E del factor implícito CRT está en t CO2/TJ; el modelo conserva kg CO2/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="75" customHeight="1">
       <x:c r="A361" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -15036,13 +15273,13 @@
         <x:v>CRT1A|2022|1.A.4.b|LIQUID_FUELS|CH4</x:v>
       </x:c>
       <x:c r="J361" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|LIQUID_FUELS|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C25 (TJ), I25 (kt CH4)</x:v>
       </x:c>
       <x:c r="K361" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="362">
+        <x:v>FE = (I25=0.091254160000000001 kt CH4 / C25=18250.831200000001 TJ) x 1000000 kg/kt; valor aplicado 5.000000219168101 kg CH4/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="75" customHeight="1">
       <x:c r="A362" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -15071,10 +15308,10 @@
         <x:v>CRT1A|2022|1.A.4.b|LIQUID_FUELS|N2O</x:v>
       </x:c>
       <x:c r="J362" s="73" t="str">
-        <x:v>Table1.A(a)s4; registro CRT1A|2022|1.A.4.b|LIQUID_FUELS|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.A(a)s4!C25 (TJ), J25 (kt N2O)</x:v>
       </x:c>
       <x:c r="K362" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1a_quema_combustibles_1990_2022_v01.csv.</x:v>
+        <x:v>FE = (J25=0.00182508 kt N2O / C25=18250.831200000001 TJ) x 1000000 kg/kt; valor aplicado 0.09999982904888188 kg N2O/TJ. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -16127,7 +16364,7 @@
         <x:v>Se conserva el estado NO porque la fuente no aporta un factor numérico para la clave interna FE_NO|2022|1.B.2.b.ii|NO|N2O.</x:v>
       </x:c>
     </x:row>
-    <x:row r="393">
+    <x:row r="393" ht="87" customHeight="1">
       <x:c r="A393" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -16156,13 +16393,13 @@
         <x:v>CRT1B2|2022|1.B.2.a.ii|CO2</x:v>
       </x:c>
       <x:c r="J393" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2022|1.B.2.a.ii|CO2</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.B.2!I12 (kt CO2); denominador PSUT BEV2_01093</x:v>
       </x:c>
       <x:c r="K393" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="394">
+        <x:v>FE = (I12=0.000051523 kt CO2 / extracción PSUT BEV2_01093=7611.5067 TJ) x 1000000 kg/kt; valor aplicado 0.0067690934306081614 kg CO2/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="87" customHeight="1">
       <x:c r="A394" s="72" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -16191,13 +16428,13 @@
         <x:v>CRT1B2|2022|1.B.2.a.ii|CH4</x:v>
       </x:c>
       <x:c r="J394" s="73" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2022|1.B.2.a.ii|CH4</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.B.2!J12 (kt CH4); denominador PSUT BEV2_01093</x:v>
       </x:c>
       <x:c r="K394" s="74" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="395">
+        <x:v>FE = (J12=0.00070694 kt CH4 / extracción PSUT BEV2_01093=7611.5067 TJ) x 1000000 kg/kt; valor aplicado 0.09287780039660215 kg CH4/TJ. Corresponde solo a producción y mejoramiento 1.B.2.a.ii; no incorpora refinación/almacenamiento 1.B.2.a.iv, cuyo CH4 está en J14. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="75" customHeight="1">
       <x:c r="A395" s="75" t="str">
         <x:v>FACTOR_EMISION_OBS</x:v>
       </x:c>
@@ -16217,7 +16454,7 @@
         <x:v>N2O</x:v>
       </x:c>
       <x:c r="G395" s="76" t="str">
-        <x:v>observacion_externa</x:v>
+        <x:v>clave_no_sin_valor_numerico</x:v>
       </x:c>
       <x:c r="H395" s="76" t="str">
         <x:v>UNFCCC_GTM_CRT_2024</x:v>
@@ -16226,10 +16463,1373 @@
         <x:v>CRT1B2|2022|1.B.2.a.ii|N2O</x:v>
       </x:c>
       <x:c r="J395" s="76" t="str">
-        <x:v>Table1.B.2; registro CRT1B2|2022|1.B.2.a.ii|N2O</x:v>
+        <x:v>marn_2025_crt_v03_2022.xlsx; Table1.B.2!K12 (kt N2O); denominador PSUT BEV2_01093</x:v>
       </x:c>
       <x:c r="K395" s="77" t="str">
-        <x:v>Localizador recuperado del archivo de extracción emisiones_crt_tabla_1b2_fugitivas_petroleo_gas_1990_2022_v01.csv.</x:v>
+        <x:v>La celda K12 de emisiones N2O y H12 del factor fuente están vacías. NO es la notación interna conservada por el modelo para ausencia numérica; no se transcribió un NO literal de K12 y no representa una emisión igual a cero. Cotejo directo 2026-09-06; archivo marn_2025_crt_v03_2022.xlsx; SHA-256 55ea0ebf9c029a3bbd56aa5b6faff643d67df4d0b3987e778786d73d18c4d22e.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="64" customHeight="1">
+      <x:c r="A396" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B396" s="68" t="str">
+        <x:v>BEV2_00007</x:v>
+      </x:c>
+      <x:c r="C396" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D396" s="68" t="str"/>
+      <x:c r="E396" s="68" t="str"/>
+      <x:c r="F396" s="68" t="str"/>
+      <x:c r="G396" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H396" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I396" s="68" t="str">
+        <x:v>BEV2_00007</x:v>
+      </x:c>
+      <x:c r="J396" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 6, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K396" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-2520.2 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="64" customHeight="1">
+      <x:c r="A397" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B397" s="68" t="str">
+        <x:v>BEV2_00094</x:v>
+      </x:c>
+      <x:c r="C397" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D397" s="68" t="str"/>
+      <x:c r="E397" s="68" t="str"/>
+      <x:c r="F397" s="68" t="str"/>
+      <x:c r="G397" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H397" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I397" s="68" t="str">
+        <x:v>BEV2_00094</x:v>
+      </x:c>
+      <x:c r="J397" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 6, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K397" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=48375.61 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="64" customHeight="1">
+      <x:c r="A398" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B398" s="68" t="str">
+        <x:v>BEV2_00142</x:v>
+      </x:c>
+      <x:c r="C398" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D398" s="68" t="str"/>
+      <x:c r="E398" s="68" t="str"/>
+      <x:c r="F398" s="68" t="str"/>
+      <x:c r="G398" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H398" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I398" s="68" t="str">
+        <x:v>BEV2_00142</x:v>
+      </x:c>
+      <x:c r="J398" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 7, tabla 2 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K398" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=11790.56 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="64" customHeight="1">
+      <x:c r="A399" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B399" s="68" t="str">
+        <x:v>BEV2_00160</x:v>
+      </x:c>
+      <x:c r="C399" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D399" s="68" t="str"/>
+      <x:c r="E399" s="68" t="str"/>
+      <x:c r="F399" s="68" t="str"/>
+      <x:c r="G399" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H399" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I399" s="68" t="str">
+        <x:v>BEV2_00160</x:v>
+      </x:c>
+      <x:c r="J399" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 7, tabla 2 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K399" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=8105.61 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="64" customHeight="1">
+      <x:c r="A400" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B400" s="68" t="str">
+        <x:v>BEV2_00161</x:v>
+      </x:c>
+      <x:c r="C400" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D400" s="68" t="str"/>
+      <x:c r="E400" s="68" t="str"/>
+      <x:c r="F400" s="68" t="str"/>
+      <x:c r="G400" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H400" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I400" s="68" t="str">
+        <x:v>BEV2_00161</x:v>
+      </x:c>
+      <x:c r="J400" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 7, tabla 2 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K400" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=647.8 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="64" customHeight="1">
+      <x:c r="A401" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B401" s="68" t="str">
+        <x:v>BEV2_00184</x:v>
+      </x:c>
+      <x:c r="C401" s="68" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D401" s="68" t="str"/>
+      <x:c r="E401" s="68" t="str"/>
+      <x:c r="F401" s="68" t="str"/>
+      <x:c r="G401" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H401" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I401" s="68" t="str">
+        <x:v>BEV2_00184</x:v>
+      </x:c>
+      <x:c r="J401" s="68" t="str">
+        <x:v>mem_2018_balance_energetico.pdf; página PDF 7, tabla 2 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K401" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=12343.03 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2018_balance_energetico.pdf; SHA-256 c8344b1996c562a801b47bde282e563eb24d285a7d89a9fcfdbc910ceb110627.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="64" customHeight="1">
+      <x:c r="A402" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B402" s="68" t="str">
+        <x:v>BEV2_00245</x:v>
+      </x:c>
+      <x:c r="C402" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D402" s="68" t="str"/>
+      <x:c r="E402" s="68" t="str"/>
+      <x:c r="F402" s="68" t="str"/>
+      <x:c r="G402" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H402" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I402" s="68" t="str">
+        <x:v>BEV2_00245</x:v>
+      </x:c>
+      <x:c r="J402" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 7, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K402" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-771.95 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="64" customHeight="1">
+      <x:c r="A403" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B403" s="68" t="str">
+        <x:v>BEV2_00332</x:v>
+      </x:c>
+      <x:c r="C403" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D403" s="68" t="str"/>
+      <x:c r="E403" s="68" t="str"/>
+      <x:c r="F403" s="68" t="str"/>
+      <x:c r="G403" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H403" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I403" s="68" t="str">
+        <x:v>BEV2_00332</x:v>
+      </x:c>
+      <x:c r="J403" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 7, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K403" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=49305.49 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="64" customHeight="1">
+      <x:c r="A404" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B404" s="68" t="str">
+        <x:v>BEV2_00380</x:v>
+      </x:c>
+      <x:c r="C404" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D404" s="68" t="str"/>
+      <x:c r="E404" s="68" t="str"/>
+      <x:c r="F404" s="68" t="str"/>
+      <x:c r="G404" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H404" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I404" s="68" t="str">
+        <x:v>BEV2_00380</x:v>
+      </x:c>
+      <x:c r="J404" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K404" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=13520.33 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="64" customHeight="1">
+      <x:c r="A405" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B405" s="68" t="str">
+        <x:v>BEV2_00398</x:v>
+      </x:c>
+      <x:c r="C405" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D405" s="68" t="str"/>
+      <x:c r="E405" s="68" t="str"/>
+      <x:c r="F405" s="68" t="str"/>
+      <x:c r="G405" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H405" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I405" s="68" t="str">
+        <x:v>BEV2_00398</x:v>
+      </x:c>
+      <x:c r="J405" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K405" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=7915.54 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="64" customHeight="1">
+      <x:c r="A406" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B406" s="68" t="str">
+        <x:v>BEV2_00399</x:v>
+      </x:c>
+      <x:c r="C406" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D406" s="68" t="str"/>
+      <x:c r="E406" s="68" t="str"/>
+      <x:c r="F406" s="68" t="str"/>
+      <x:c r="G406" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H406" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I406" s="68" t="str">
+        <x:v>BEV2_00399</x:v>
+      </x:c>
+      <x:c r="J406" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K406" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=810.44 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="103" customHeight="1">
+      <x:c r="A407" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B407" s="68" t="str">
+        <x:v>BEV2_00422</x:v>
+      </x:c>
+      <x:c r="C407" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D407" s="68" t="str"/>
+      <x:c r="E407" s="68" t="str"/>
+      <x:c r="F407" s="68" t="str"/>
+      <x:c r="G407" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H407" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I407" s="68" t="str">
+        <x:v>BEV2_00422</x:v>
+      </x:c>
+      <x:c r="J407" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K407" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=14162.48 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="103" customHeight="1">
+      <x:c r="A408" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B408" s="68" t="str">
+        <x:v>BEV2_00423</x:v>
+      </x:c>
+      <x:c r="C408" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D408" s="68" t="str"/>
+      <x:c r="E408" s="68" t="str"/>
+      <x:c r="F408" s="68" t="str"/>
+      <x:c r="G408" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H408" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I408" s="68" t="str">
+        <x:v>BEV2_00423</x:v>
+      </x:c>
+      <x:c r="J408" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Exportación / GAS</x:v>
+      </x:c>
+      <x:c r="K408" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=291.72 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="103" customHeight="1">
+      <x:c r="A409" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B409" s="68" t="str">
+        <x:v>BEV2_00424</x:v>
+      </x:c>
+      <x:c r="C409" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D409" s="68" t="str"/>
+      <x:c r="E409" s="68" t="str"/>
+      <x:c r="F409" s="68" t="str"/>
+      <x:c r="G409" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H409" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I409" s="68" t="str">
+        <x:v>BEV2_00424</x:v>
+      </x:c>
+      <x:c r="J409" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Variación inventario / GAS</x:v>
+      </x:c>
+      <x:c r="K409" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-414.51 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="103" customHeight="1">
+      <x:c r="A410" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B410" s="68" t="str">
+        <x:v>BEV2_00429</x:v>
+      </x:c>
+      <x:c r="C410" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D410" s="68" t="str"/>
+      <x:c r="E410" s="68" t="str"/>
+      <x:c r="F410" s="68" t="str"/>
+      <x:c r="G410" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H410" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I410" s="68" t="str">
+        <x:v>BEV2_00429</x:v>
+      </x:c>
+      <x:c r="J410" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Transporte / GAS</x:v>
+      </x:c>
+      <x:c r="K410" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=11278.12 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="103" customHeight="1">
+      <x:c r="A411" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B411" s="68" t="str">
+        <x:v>BEV2_00431</x:v>
+      </x:c>
+      <x:c r="C411" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D411" s="68" t="str"/>
+      <x:c r="E411" s="68" t="str"/>
+      <x:c r="F411" s="68" t="str"/>
+      <x:c r="G411" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H411" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I411" s="68" t="str">
+        <x:v>BEV2_00431</x:v>
+      </x:c>
+      <x:c r="J411" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Comercio y servicios / GAS</x:v>
+      </x:c>
+      <x:c r="K411" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=57.78 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="103" customHeight="1">
+      <x:c r="A412" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B412" s="68" t="str">
+        <x:v>BEV2_00432</x:v>
+      </x:c>
+      <x:c r="C412" s="68" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D412" s="68" t="str"/>
+      <x:c r="E412" s="68" t="str"/>
+      <x:c r="F412" s="68" t="str"/>
+      <x:c r="G412" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H412" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I412" s="68" t="str">
+        <x:v>BEV2_00432</x:v>
+      </x:c>
+      <x:c r="J412" s="68" t="str">
+        <x:v>mem_2019_balance_energetico.pdf; página PDF 8, tabla 2 (base 1); Industria / GAS</x:v>
+      </x:c>
+      <x:c r="K412" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=231.13 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. BEN 2019: tabla 2, PDF p.8, oferta GAS 13456.25 kBEP frente a usos sectoriales 11567.03 kBEP; tabla 5, PDF p.11, repite GAS 13456.25 kBEP. La diferencia 1889.22 kBEP (10976.3682 TJ) se mantiene en NO_ASIG; contradicción publicada, sin elección de una cifra sustituta. Cotejo directo 2026-09-06; archivo mem_2019_balance_energetico.pdf; SHA-256 e903c6822590b153ddf138ad77bbea4dfa412fcd7f8d1d9d91d4acbdcebb8a86.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="64" customHeight="1">
+      <x:c r="A413" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B413" s="68" t="str">
+        <x:v>BEV2_00497</x:v>
+      </x:c>
+      <x:c r="C413" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D413" s="68" t="str"/>
+      <x:c r="E413" s="68" t="str"/>
+      <x:c r="F413" s="68" t="str"/>
+      <x:c r="G413" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H413" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I413" s="68" t="str">
+        <x:v>BEV2_00497</x:v>
+      </x:c>
+      <x:c r="J413" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 8, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K413" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-1139.8 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="64" customHeight="1">
+      <x:c r="A414" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B414" s="68" t="str">
+        <x:v>BEV2_00584</x:v>
+      </x:c>
+      <x:c r="C414" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D414" s="68" t="str"/>
+      <x:c r="E414" s="68" t="str"/>
+      <x:c r="F414" s="68" t="str"/>
+      <x:c r="G414" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H414" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I414" s="68" t="str">
+        <x:v>BEV2_00584</x:v>
+      </x:c>
+      <x:c r="J414" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 8, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K414" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=50791.82 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="64" customHeight="1">
+      <x:c r="A415" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B415" s="68" t="str">
+        <x:v>BEV2_00632</x:v>
+      </x:c>
+      <x:c r="C415" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D415" s="68" t="str"/>
+      <x:c r="E415" s="68" t="str"/>
+      <x:c r="F415" s="68" t="str"/>
+      <x:c r="G415" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H415" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I415" s="68" t="str">
+        <x:v>BEV2_00632</x:v>
+      </x:c>
+      <x:c r="J415" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 9, tabla 2 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K415" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=11949.87 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="64" customHeight="1">
+      <x:c r="A416" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B416" s="68" t="str">
+        <x:v>BEV2_00650</x:v>
+      </x:c>
+      <x:c r="C416" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D416" s="68" t="str"/>
+      <x:c r="E416" s="68" t="str"/>
+      <x:c r="F416" s="68" t="str"/>
+      <x:c r="G416" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H416" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I416" s="68" t="str">
+        <x:v>BEV2_00650</x:v>
+      </x:c>
+      <x:c r="J416" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 9, tabla 2 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K416" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=7400.48 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="64" customHeight="1">
+      <x:c r="A417" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B417" s="68" t="str">
+        <x:v>BEV2_00651</x:v>
+      </x:c>
+      <x:c r="C417" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D417" s="68" t="str"/>
+      <x:c r="E417" s="68" t="str"/>
+      <x:c r="F417" s="68" t="str"/>
+      <x:c r="G417" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H417" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I417" s="68" t="str">
+        <x:v>BEV2_00651</x:v>
+      </x:c>
+      <x:c r="J417" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 9, tabla 2 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K417" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=532.14 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="64" customHeight="1">
+      <x:c r="A418" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B418" s="68" t="str">
+        <x:v>BEV2_00674</x:v>
+      </x:c>
+      <x:c r="C418" s="68" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D418" s="68" t="str"/>
+      <x:c r="E418" s="68" t="str"/>
+      <x:c r="F418" s="68" t="str"/>
+      <x:c r="G418" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H418" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I418" s="68" t="str">
+        <x:v>BEV2_00674</x:v>
+      </x:c>
+      <x:c r="J418" s="68" t="str">
+        <x:v>mem_2020_balance_energetico.pdf; página PDF 9, tabla 2 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K418" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=12417.95 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2020_balance_energetico.pdf; SHA-256 840c9d30764fe670c9f4d2f3551ca1fb432570a150bec146a67d6c55fca3cfb0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="64" customHeight="1">
+      <x:c r="A419" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B419" s="68" t="str">
+        <x:v>BEV2_00735</x:v>
+      </x:c>
+      <x:c r="C419" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D419" s="68" t="str"/>
+      <x:c r="E419" s="68" t="str"/>
+      <x:c r="F419" s="68" t="str"/>
+      <x:c r="G419" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H419" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I419" s="68" t="str">
+        <x:v>BEV2_00735</x:v>
+      </x:c>
+      <x:c r="J419" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K419" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-5556.35 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="64" customHeight="1">
+      <x:c r="A420" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B420" s="68" t="str">
+        <x:v>BEV2_00836</x:v>
+      </x:c>
+      <x:c r="C420" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D420" s="68" t="str"/>
+      <x:c r="E420" s="68" t="str"/>
+      <x:c r="F420" s="68" t="str"/>
+      <x:c r="G420" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H420" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I420" s="68" t="str">
+        <x:v>BEV2_00836</x:v>
+      </x:c>
+      <x:c r="J420" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K420" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=52322.96 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="64" customHeight="1">
+      <x:c r="A421" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B421" s="68" t="str">
+        <x:v>BEV2_00884</x:v>
+      </x:c>
+      <x:c r="C421" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D421" s="68" t="str"/>
+      <x:c r="E421" s="68" t="str"/>
+      <x:c r="F421" s="68" t="str"/>
+      <x:c r="G421" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H421" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I421" s="68" t="str">
+        <x:v>BEV2_00884</x:v>
+      </x:c>
+      <x:c r="J421" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 12, tabla 2 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K421" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=14645.03 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="64" customHeight="1">
+      <x:c r="A422" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B422" s="68" t="str">
+        <x:v>BEV2_00902</x:v>
+      </x:c>
+      <x:c r="C422" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D422" s="68" t="str"/>
+      <x:c r="E422" s="68" t="str"/>
+      <x:c r="F422" s="68" t="str"/>
+      <x:c r="G422" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H422" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I422" s="68" t="str">
+        <x:v>BEV2_00902</x:v>
+      </x:c>
+      <x:c r="J422" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 12, tabla 2 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K422" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=8242.4 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="64" customHeight="1">
+      <x:c r="A423" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B423" s="68" t="str">
+        <x:v>BEV2_00903</x:v>
+      </x:c>
+      <x:c r="C423" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D423" s="68" t="str"/>
+      <x:c r="E423" s="68" t="str"/>
+      <x:c r="F423" s="68" t="str"/>
+      <x:c r="G423" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H423" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I423" s="68" t="str">
+        <x:v>BEV2_00903</x:v>
+      </x:c>
+      <x:c r="J423" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 12, tabla 2 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K423" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=672.37 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="64" customHeight="1">
+      <x:c r="A424" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B424" s="68" t="str">
+        <x:v>BEV2_00926</x:v>
+      </x:c>
+      <x:c r="C424" s="68" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D424" s="68" t="str"/>
+      <x:c r="E424" s="68" t="str"/>
+      <x:c r="F424" s="68" t="str"/>
+      <x:c r="G424" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H424" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I424" s="68" t="str">
+        <x:v>BEV2_00926</x:v>
+      </x:c>
+      <x:c r="J424" s="68" t="str">
+        <x:v>mem_2021_balance_energetico.pdf; página PDF 12, tabla 2 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K424" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=15346.16 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2021_balance_energetico.pdf; SHA-256 dd499935b414220506b02020ab74a491ec7efa0d5bc2895c5755ca135e7d7360.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="64" customHeight="1">
+      <x:c r="A425" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B425" s="68" t="str">
+        <x:v>BEV2_00987</x:v>
+      </x:c>
+      <x:c r="C425" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D425" s="68" t="str"/>
+      <x:c r="E425" s="68" t="str"/>
+      <x:c r="F425" s="68" t="str"/>
+      <x:c r="G425" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H425" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I425" s="68" t="str">
+        <x:v>BEV2_00987</x:v>
+      </x:c>
+      <x:c r="J425" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 16, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K425" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-3768.4 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="64" customHeight="1">
+      <x:c r="A426" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B426" s="68" t="str">
+        <x:v>BEV2_01088</x:v>
+      </x:c>
+      <x:c r="C426" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D426" s="68" t="str"/>
+      <x:c r="E426" s="68" t="str"/>
+      <x:c r="F426" s="68" t="str"/>
+      <x:c r="G426" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H426" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I426" s="68" t="str">
+        <x:v>BEV2_01088</x:v>
+      </x:c>
+      <x:c r="J426" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 16, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K426" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=53900.26 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="64" customHeight="1">
+      <x:c r="A427" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B427" s="68" t="str">
+        <x:v>BEV2_01136</x:v>
+      </x:c>
+      <x:c r="C427" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D427" s="68" t="str"/>
+      <x:c r="E427" s="68" t="str"/>
+      <x:c r="F427" s="68" t="str"/>
+      <x:c r="G427" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H427" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I427" s="68" t="str">
+        <x:v>BEV2_01136</x:v>
+      </x:c>
+      <x:c r="J427" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 19, tabla 3 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K427" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=14236.55 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="64" customHeight="1">
+      <x:c r="A428" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B428" s="68" t="str">
+        <x:v>BEV2_01154</x:v>
+      </x:c>
+      <x:c r="C428" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D428" s="68" t="str"/>
+      <x:c r="E428" s="68" t="str"/>
+      <x:c r="F428" s="68" t="str"/>
+      <x:c r="G428" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H428" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I428" s="68" t="str">
+        <x:v>BEV2_01154</x:v>
+      </x:c>
+      <x:c r="J428" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 19, tabla 3 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K428" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=7654.11 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="64" customHeight="1">
+      <x:c r="A429" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B429" s="68" t="str">
+        <x:v>BEV2_01155</x:v>
+      </x:c>
+      <x:c r="C429" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D429" s="68" t="str"/>
+      <x:c r="E429" s="68" t="str"/>
+      <x:c r="F429" s="68" t="str"/>
+      <x:c r="G429" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H429" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I429" s="68" t="str">
+        <x:v>BEV2_01155</x:v>
+      </x:c>
+      <x:c r="J429" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 19, tabla 3 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K429" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=492.41 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="64" customHeight="1">
+      <x:c r="A430" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B430" s="68" t="str">
+        <x:v>BEV2_01178</x:v>
+      </x:c>
+      <x:c r="C430" s="68" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D430" s="68" t="str"/>
+      <x:c r="E430" s="68" t="str"/>
+      <x:c r="F430" s="68" t="str"/>
+      <x:c r="G430" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H430" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I430" s="68" t="str">
+        <x:v>BEV2_01178</x:v>
+      </x:c>
+      <x:c r="J430" s="68" t="str">
+        <x:v>mem_2022_balance_energetico.pdf; página PDF 19, tabla 3 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K430" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=14907.38 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2022_balance_energetico.pdf; SHA-256 ebe74b5c1223d711b0bb9b22556cc84359daf5af283edd8de16ea67aea10b272.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="64" customHeight="1">
+      <x:c r="A431" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B431" s="68" t="str">
+        <x:v>BEV2_01253</x:v>
+      </x:c>
+      <x:c r="C431" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D431" s="68" t="str"/>
+      <x:c r="E431" s="68" t="str"/>
+      <x:c r="F431" s="68" t="str"/>
+      <x:c r="G431" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H431" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I431" s="68" t="str">
+        <x:v>BEV2_01253</x:v>
+      </x:c>
+      <x:c r="J431" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K431" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-5337.66 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="64" customHeight="1">
+      <x:c r="A432" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B432" s="68" t="str">
+        <x:v>BEV2_01354</x:v>
+      </x:c>
+      <x:c r="C432" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D432" s="68" t="str"/>
+      <x:c r="E432" s="68" t="str"/>
+      <x:c r="F432" s="68" t="str"/>
+      <x:c r="G432" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H432" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I432" s="68" t="str">
+        <x:v>BEV2_01354</x:v>
+      </x:c>
+      <x:c r="J432" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K432" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=55525.11 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="64" customHeight="1">
+      <x:c r="A433" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B433" s="68" t="str">
+        <x:v>BEV2_01402</x:v>
+      </x:c>
+      <x:c r="C433" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D433" s="68" t="str"/>
+      <x:c r="E433" s="68" t="str"/>
+      <x:c r="F433" s="68" t="str"/>
+      <x:c r="G433" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H433" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I433" s="68" t="str">
+        <x:v>BEV2_01402</x:v>
+      </x:c>
+      <x:c r="J433" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K433" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=15330.97 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="64" customHeight="1">
+      <x:c r="A434" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B434" s="68" t="str">
+        <x:v>BEV2_01420</x:v>
+      </x:c>
+      <x:c r="C434" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D434" s="68" t="str"/>
+      <x:c r="E434" s="68" t="str"/>
+      <x:c r="F434" s="68" t="str"/>
+      <x:c r="G434" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H434" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I434" s="68" t="str">
+        <x:v>BEV2_01420</x:v>
+      </x:c>
+      <x:c r="J434" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K434" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=7797.22 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="64" customHeight="1">
+      <x:c r="A435" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B435" s="68" t="str">
+        <x:v>BEV2_01421</x:v>
+      </x:c>
+      <x:c r="C435" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D435" s="68" t="str"/>
+      <x:c r="E435" s="68" t="str"/>
+      <x:c r="F435" s="68" t="str"/>
+      <x:c r="G435" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H435" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I435" s="68" t="str">
+        <x:v>BEV2_01421</x:v>
+      </x:c>
+      <x:c r="J435" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K435" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=642.49 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="64" customHeight="1">
+      <x:c r="A436" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B436" s="68" t="str">
+        <x:v>BEV2_01444</x:v>
+      </x:c>
+      <x:c r="C436" s="68" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D436" s="68" t="str"/>
+      <x:c r="E436" s="68" t="str"/>
+      <x:c r="F436" s="68" t="str"/>
+      <x:c r="G436" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H436" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I436" s="68" t="str">
+        <x:v>BEV2_01444</x:v>
+      </x:c>
+      <x:c r="J436" s="68" t="str">
+        <x:v>mem_2023_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K436" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=15692.78 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2023_balance_energetico.pdf; SHA-256 f95bec72f81e306d4850983d512f0ead7b3d2a832184d80627c65f8d1d21f81c.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="64" customHeight="1">
+      <x:c r="A437" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B437" s="68" t="str">
+        <x:v>BEV2_01519</x:v>
+      </x:c>
+      <x:c r="C437" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D437" s="68" t="str"/>
+      <x:c r="E437" s="68" t="str"/>
+      <x:c r="F437" s="68" t="str"/>
+      <x:c r="G437" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H437" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I437" s="68" t="str">
+        <x:v>BEV2_01519</x:v>
+      </x:c>
+      <x:c r="J437" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Autoproductores / BCAÑ</x:v>
+      </x:c>
+      <x:c r="K437" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=-4708.74 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="64" customHeight="1">
+      <x:c r="A438" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B438" s="68" t="str">
+        <x:v>BEV2_01620</x:v>
+      </x:c>
+      <x:c r="C438" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D438" s="68" t="str"/>
+      <x:c r="E438" s="68" t="str"/>
+      <x:c r="F438" s="68" t="str"/>
+      <x:c r="G438" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H438" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I438" s="68" t="str">
+        <x:v>BEV2_01620</x:v>
+      </x:c>
+      <x:c r="J438" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 9, tabla 1 (base 1); Residencial / LEÑA</x:v>
+      </x:c>
+      <x:c r="K438" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=57198.94 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="64" customHeight="1">
+      <x:c r="A439" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B439" s="68" t="str">
+        <x:v>BEV2_01668</x:v>
+      </x:c>
+      <x:c r="C439" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D439" s="68" t="str"/>
+      <x:c r="E439" s="68" t="str"/>
+      <x:c r="F439" s="68" t="str"/>
+      <x:c r="G439" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H439" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I439" s="68" t="str">
+        <x:v>BEV2_01668</x:v>
+      </x:c>
+      <x:c r="J439" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Importación / DOIL</x:v>
+      </x:c>
+      <x:c r="K439" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=16069.68 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="64" customHeight="1">
+      <x:c r="A440" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B440" s="68" t="str">
+        <x:v>BEV2_01686</x:v>
+      </x:c>
+      <x:c r="C440" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D440" s="68" t="str"/>
+      <x:c r="E440" s="68" t="str"/>
+      <x:c r="F440" s="68" t="str"/>
+      <x:c r="G440" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H440" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I440" s="68" t="str">
+        <x:v>BEV2_01686</x:v>
+      </x:c>
+      <x:c r="J440" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Centrales Eléctricas / ELEC</x:v>
+      </x:c>
+      <x:c r="K440" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=8542.76 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="64" customHeight="1">
+      <x:c r="A441" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B441" s="68" t="str">
+        <x:v>BEV2_01687</x:v>
+      </x:c>
+      <x:c r="C441" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D441" s="68" t="str"/>
+      <x:c r="E441" s="68" t="str"/>
+      <x:c r="F441" s="68" t="str"/>
+      <x:c r="G441" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H441" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I441" s="68" t="str">
+        <x:v>BEV2_01687</x:v>
+      </x:c>
+      <x:c r="J441" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Autoproductores / ELEC</x:v>
+      </x:c>
+      <x:c r="K441" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=615.49 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="64" customHeight="1">
+      <x:c r="A442" s="68" t="str">
+        <x:v>BALANCE</x:v>
+      </x:c>
+      <x:c r="B442" s="68" t="str">
+        <x:v>BEV2_01710</x:v>
+      </x:c>
+      <x:c r="C442" s="68" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D442" s="68" t="str"/>
+      <x:c r="E442" s="68" t="str"/>
+      <x:c r="F442" s="68" t="str"/>
+      <x:c r="G442" s="68" t="str">
+        <x:v>observacion_externa</x:v>
+      </x:c>
+      <x:c r="H442" s="68" t="str">
+        <x:v>MEM_BEN</x:v>
+      </x:c>
+      <x:c r="I442" s="68" t="str">
+        <x:v>BEV2_01710</x:v>
+      </x:c>
+      <x:c r="J442" s="68" t="str">
+        <x:v>mem_2024_balance_energetico.pdf; página PDF 12, tabla 3 (base 1); Importación / GAS</x:v>
+      </x:c>
+      <x:c r="K442" s="68" t="str">
+        <x:v>Cotejo visual de la celda: fuente=16855.97 kBEP, coincide con BALANCE. Forma parte de una muestra dirigida; no acredita revisión exhaustiva del balance. Cotejo directo 2026-09-06; archivo mem_2024_balance_energetico.pdf; SHA-256 515af59a6f19628e208768405489316feea277572fa7f17270233941cd50d38b.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16239,7 +17839,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b54b2445b0246c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad5fb04fca5640e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>